--- a/Resultados de la votación 2021.xlsx
+++ b/Resultados de la votación 2021.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\loren\Dropbox\MVL\RESULTADOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f5fa8a9efe53b17c/Documentos/TP FINAL DATOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCCC4F1F-83B2-4363-BB09-652BA17019C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="-204" yWindow="6420" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -25,8 +25,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1377,7 +1381,7 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1410,20 +1414,13 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1433,9 +1430,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1444,15 +1438,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2418,242 +2406,241 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J218"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" style="3" customWidth="1"/>
-    <col min="3" max="4" width="13.7109375" style="16" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
-    <col min="6" max="6" width="36.85546875" customWidth="1"/>
-    <col min="7" max="7" width="42.42578125" customWidth="1"/>
+    <col min="1" max="1" width="9.33203125" style="3" customWidth="1"/>
+    <col min="2" max="4" width="13.6640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
+    <col min="6" max="6" width="36.88671875" customWidth="1"/>
+    <col min="7" max="7" width="42.44140625" customWidth="1"/>
     <col min="8" max="8" width="17" style="2" customWidth="1"/>
-    <col min="9" max="9" width="41.85546875" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" style="2" customWidth="1"/>
+    <col min="9" max="9" width="41.88671875" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="1" customFormat="1" ht="75" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A1" s="35" t="s">
         <v>398</v>
       </c>
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="35" t="s">
         <v>397</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="35" t="s">
         <v>399</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="35" t="s">
         <v>400</v>
       </c>
-      <c r="E1" s="41" t="s">
+      <c r="E1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="41" t="s">
+      <c r="F1" s="35" t="s">
         <v>408</v>
       </c>
-      <c r="G1" s="41" t="s">
+      <c r="G1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="42" t="s">
+      <c r="H1" s="36" t="s">
         <v>403</v>
       </c>
-      <c r="I1" s="41" t="s">
+      <c r="I1" s="35" t="s">
         <v>404</v>
       </c>
-      <c r="J1" s="41" t="s">
+      <c r="J1" s="35" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="17">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="16">
         <v>7</v>
       </c>
-      <c r="B2" s="17">
+      <c r="B2" s="16">
         <v>332</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="16">
         <v>1</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="H2" s="43">
+      <c r="H2" s="37">
         <v>5000000</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="I2" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J2" s="14"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="17">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="16">
         <v>13</v>
       </c>
-      <c r="B3" s="17">
+      <c r="B3" s="16">
         <v>99</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="16">
         <v>2</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="D3" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="H3" s="43">
+      <c r="H3" s="37">
         <v>2680000</v>
       </c>
-      <c r="I3" s="18" t="s">
+      <c r="I3" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J3" s="14"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="17">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="16">
         <v>18</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="16">
         <v>94</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="16">
         <v>3</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="D4" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="18" t="s">
+      <c r="G4" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="43">
+      <c r="H4" s="37">
         <v>5000000</v>
       </c>
-      <c r="I4" s="18" t="s">
+      <c r="I4" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J4" s="14"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="17">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="16">
         <v>5</v>
       </c>
-      <c r="B5" s="17">
+      <c r="B5" s="16">
         <v>92</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="16">
         <v>4</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="G5" s="18" t="s">
+      <c r="G5" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="H5" s="43">
+      <c r="H5" s="37">
         <v>2100000</v>
       </c>
-      <c r="I5" s="18" t="s">
+      <c r="I5" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J5" s="14"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="17">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="16">
         <v>12</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="16">
         <v>90</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="16">
         <v>5</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="H6" s="43">
+      <c r="H6" s="37">
         <v>2435000</v>
       </c>
-      <c r="I6" s="18" t="s">
+      <c r="I6" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J6" s="14"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="19">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="18">
         <v>4</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="18">
         <v>71</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="18">
         <v>6</v>
       </c>
-      <c r="D7" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="E7" s="21" t="s">
+      <c r="D7" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="G7" s="21" t="s">
+      <c r="G7" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="21">
         <v>2200000</v>
       </c>
-      <c r="I7" s="21" t="s">
+      <c r="I7" s="5" t="s">
         <v>407</v>
       </c>
       <c r="J7" s="14"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="20">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="18">
         <v>17</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="18">
         <v>22</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="18">
         <v>7</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E8" s="5" t="s">
@@ -2673,17 +2660,17 @@
       </c>
       <c r="J8" s="14"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="20">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="18">
         <v>15</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="18">
         <v>22</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="18">
         <v>8</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E9" s="5" t="s">
@@ -2703,89 +2690,89 @@
       </c>
       <c r="J9" s="14"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="17">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="16">
         <v>16</v>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="16">
         <v>20</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="16">
         <v>9</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="18" t="s">
+      <c r="G10" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="H10" s="43">
+      <c r="H10" s="37">
         <v>630000</v>
       </c>
-      <c r="I10" s="18" t="s">
+      <c r="I10" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J10" s="14"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="17">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="16">
         <v>14</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="16">
         <v>20</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="16">
         <v>10</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="G11" s="18" t="s">
+      <c r="G11" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="H11" s="43">
+      <c r="H11" s="37">
         <v>429000</v>
       </c>
-      <c r="I11" s="18" t="s">
+      <c r="I11" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J11" s="14"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="19">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="18">
         <v>1</v>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="18">
         <v>14</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="18">
         <v>11</v>
       </c>
-      <c r="D12" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="E12" s="21" t="s">
+      <c r="D12" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="F12" s="21" t="s">
+      <c r="F12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="21" t="s">
+      <c r="G12" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="H12" s="24">
+      <c r="H12" s="21">
         <v>226650</v>
       </c>
       <c r="I12" s="5" t="s">
@@ -2793,50 +2780,50 @@
       </c>
       <c r="J12" s="14"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="17">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="16">
         <v>6</v>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="16">
         <v>12</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="16">
         <v>12</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="F13" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="G13" s="18" t="s">
+      <c r="G13" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="H13" s="43">
+      <c r="H13" s="37">
         <v>104400</v>
       </c>
-      <c r="I13" s="18" t="s">
+      <c r="I13" s="17" t="s">
         <v>406</v>
       </c>
-      <c r="J13" s="22">
+      <c r="J13" s="19">
         <f>SUM(H2:H6,H10:H11,H13)</f>
         <v>18378400</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="20">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="18">
         <v>2</v>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="18">
         <v>11</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="18">
         <v>13</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E14" s="5" t="s">
@@ -2856,17 +2843,17 @@
       </c>
       <c r="J14" s="14"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="20">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="18">
         <v>8</v>
       </c>
-      <c r="B15" s="20">
+      <c r="B15" s="18">
         <v>9</v>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="18">
         <v>14</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E15" s="5" t="s">
@@ -2886,17 +2873,17 @@
       </c>
       <c r="J15" s="14"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="20">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="18">
         <v>9</v>
       </c>
-      <c r="B16" s="20">
+      <c r="B16" s="18">
         <v>9</v>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="18">
         <v>15</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E16" s="5" t="s">
@@ -2916,17 +2903,17 @@
       </c>
       <c r="J16" s="14"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="20">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="18">
         <v>10</v>
       </c>
-      <c r="B17" s="20">
+      <c r="B17" s="18">
         <v>6</v>
       </c>
-      <c r="C17" s="19">
+      <c r="C17" s="18">
         <v>16</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E17" s="5" t="s">
@@ -2946,17 +2933,17 @@
       </c>
       <c r="J17" s="14"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="20">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="18">
         <v>11</v>
       </c>
-      <c r="B18" s="20">
+      <c r="B18" s="18">
         <v>5</v>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="18">
         <v>17</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E18" s="5" t="s">
@@ -2976,317 +2963,317 @@
       </c>
       <c r="J18" s="14"/>
     </row>
-    <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="31">
+    <row r="19" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="27">
         <v>3</v>
       </c>
-      <c r="B19" s="32">
+      <c r="B19" s="27">
         <v>3</v>
       </c>
-      <c r="C19" s="32">
+      <c r="C19" s="27">
         <v>18</v>
       </c>
-      <c r="D19" s="32" t="s">
-        <v>402</v>
-      </c>
-      <c r="E19" s="33" t="s">
+      <c r="D19" s="27" t="s">
+        <v>402</v>
+      </c>
+      <c r="E19" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="F19" s="33" t="s">
+      <c r="F19" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="G19" s="33" t="s">
+      <c r="G19" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="H19" s="34">
+      <c r="H19" s="29">
         <v>615000</v>
       </c>
-      <c r="I19" s="33" t="s">
-        <v>407</v>
-      </c>
-      <c r="J19" s="34"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="28">
+      <c r="I19" s="28" t="s">
+        <v>407</v>
+      </c>
+      <c r="J19" s="29"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="24">
         <v>18</v>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="24">
         <v>210</v>
       </c>
-      <c r="C20" s="28">
+      <c r="C20" s="24">
         <v>1</v>
       </c>
-      <c r="D20" s="28" t="s">
+      <c r="D20" s="24" t="s">
         <v>401</v>
       </c>
-      <c r="E20" s="29" t="s">
+      <c r="E20" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="F20" s="29" t="s">
+      <c r="F20" s="25" t="s">
         <v>201</v>
       </c>
-      <c r="G20" s="29" t="s">
+      <c r="G20" s="25" t="s">
         <v>202</v>
       </c>
-      <c r="H20" s="44">
+      <c r="H20" s="38">
         <v>1700000</v>
       </c>
-      <c r="I20" s="29" t="s">
+      <c r="I20" s="25" t="s">
         <v>406</v>
       </c>
-      <c r="J20" s="30"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="17">
+      <c r="J20" s="26"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="16">
         <v>1</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="16">
         <v>180</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="16">
         <v>2</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E21" s="18" t="s">
+      <c r="E21" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="F21" s="18" t="s">
+      <c r="F21" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="G21" s="18" t="s">
+      <c r="G21" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="H21" s="43">
+      <c r="H21" s="37">
         <v>5000000</v>
       </c>
-      <c r="I21" s="18" t="s">
+      <c r="I21" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J21" s="14"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="17">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="16">
         <v>6</v>
       </c>
-      <c r="B22" s="17">
+      <c r="B22" s="16">
         <v>163</v>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="16">
         <v>3</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="F22" s="18" t="s">
+      <c r="F22" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="G22" s="18" t="s">
+      <c r="G22" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="H22" s="43">
+      <c r="H22" s="37">
         <v>5000000</v>
       </c>
-      <c r="I22" s="18" t="s">
+      <c r="I22" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J22" s="14"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="17">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="16">
         <v>17</v>
       </c>
-      <c r="B23" s="17">
+      <c r="B23" s="16">
         <v>156</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="16">
         <v>4</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E23" s="18" t="s">
+      <c r="E23" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="F23" s="18" t="s">
+      <c r="F23" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="G23" s="18" t="s">
+      <c r="G23" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="H23" s="43">
+      <c r="H23" s="37">
         <v>4387000</v>
       </c>
-      <c r="I23" s="18" t="s">
+      <c r="I23" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J23" s="14"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="17">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="16">
         <v>11</v>
       </c>
-      <c r="B24" s="17">
+      <c r="B24" s="16">
         <v>129</v>
       </c>
-      <c r="C24" s="17">
+      <c r="C24" s="16">
         <v>5</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="D24" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="F24" s="18" t="s">
+      <c r="F24" s="17" t="s">
         <v>210</v>
       </c>
-      <c r="G24" s="18" t="s">
+      <c r="G24" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="H24" s="43">
+      <c r="H24" s="37">
         <v>1000000</v>
       </c>
-      <c r="I24" s="18" t="s">
+      <c r="I24" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J24" s="14"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="17">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="16">
         <v>10</v>
       </c>
-      <c r="B25" s="17">
+      <c r="B25" s="16">
         <v>115</v>
       </c>
-      <c r="C25" s="17">
+      <c r="C25" s="16">
         <v>6</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E25" s="18" t="s">
+      <c r="E25" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="F25" s="18" t="s">
+      <c r="F25" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="G25" s="18" t="s">
+      <c r="G25" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="H25" s="43">
+      <c r="H25" s="37">
         <v>2500000</v>
       </c>
-      <c r="I25" s="18" t="s">
+      <c r="I25" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J25" s="14"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="17">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" s="16">
         <v>5</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B26" s="16">
         <v>107</v>
       </c>
-      <c r="C26" s="17">
+      <c r="C26" s="16">
         <v>7</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="E26" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="F26" s="18" t="s">
+      <c r="F26" s="17" t="s">
         <v>213</v>
       </c>
-      <c r="G26" s="18" t="s">
+      <c r="G26" s="17" t="s">
         <v>214</v>
       </c>
-      <c r="H26" s="43">
+      <c r="H26" s="37">
         <v>2300000</v>
       </c>
-      <c r="I26" s="18" t="s">
+      <c r="I26" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J26" s="14"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="17">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="16">
         <v>8</v>
       </c>
-      <c r="B27" s="17">
+      <c r="B27" s="16">
         <v>103</v>
       </c>
-      <c r="C27" s="17">
+      <c r="C27" s="16">
         <v>8</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="D27" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="F27" s="18" t="s">
+      <c r="F27" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="G27" s="18" t="s">
+      <c r="G27" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="H27" s="43">
+      <c r="H27" s="37">
         <v>1560750</v>
       </c>
-      <c r="I27" s="18" t="s">
+      <c r="I27" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J27" s="14"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="17">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="16">
         <v>16</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B28" s="16">
         <v>102</v>
       </c>
-      <c r="C28" s="17">
+      <c r="C28" s="16">
         <v>9</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D28" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E28" s="18" t="s">
+      <c r="E28" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="F28" s="18" t="s">
+      <c r="F28" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="G28" s="18" t="s">
+      <c r="G28" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="H28" s="43">
+      <c r="H28" s="37">
         <v>2175000</v>
       </c>
-      <c r="I28" s="18" t="s">
+      <c r="I28" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J28" s="14"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="20">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="18">
         <v>9</v>
       </c>
-      <c r="B29" s="19">
+      <c r="B29" s="18">
         <v>91</v>
       </c>
-      <c r="C29" s="19">
+      <c r="C29" s="18">
         <v>10</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="D29" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E29" s="5" t="s">
@@ -3306,50 +3293,50 @@
       </c>
       <c r="J29" s="14"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="17">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="16">
         <v>14</v>
       </c>
-      <c r="B30" s="17">
+      <c r="B30" s="16">
         <v>55</v>
       </c>
-      <c r="C30" s="17">
+      <c r="C30" s="16">
         <v>11</v>
       </c>
-      <c r="D30" s="17" t="s">
+      <c r="D30" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E30" s="18" t="s">
+      <c r="E30" s="17" t="s">
         <v>191</v>
       </c>
-      <c r="F30" s="18" t="s">
+      <c r="F30" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="G30" s="18" t="s">
+      <c r="G30" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="H30" s="43">
+      <c r="H30" s="37">
         <v>343200</v>
       </c>
-      <c r="I30" s="18" t="s">
+      <c r="I30" s="17" t="s">
         <v>406</v>
       </c>
-      <c r="J30" s="22">
+      <c r="J30" s="19">
         <f>SUM(H20:H28,H30)</f>
         <v>25965950</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="20">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A31" s="18">
         <v>13</v>
       </c>
-      <c r="B31" s="19">
+      <c r="B31" s="18">
         <v>44</v>
       </c>
-      <c r="C31" s="19">
+      <c r="C31" s="18">
         <v>12</v>
       </c>
-      <c r="D31" s="19" t="s">
+      <c r="D31" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E31" s="5" t="s">
@@ -3369,17 +3356,17 @@
       </c>
       <c r="J31" s="14"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="20">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A32" s="18">
         <v>3</v>
       </c>
-      <c r="B32" s="19">
+      <c r="B32" s="18">
         <v>33</v>
       </c>
-      <c r="C32" s="19">
+      <c r="C32" s="18">
         <v>13</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="D32" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E32" s="5" t="s">
@@ -3399,17 +3386,17 @@
       </c>
       <c r="J32" s="14"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="20">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A33" s="18">
         <v>2</v>
       </c>
-      <c r="B33" s="19">
+      <c r="B33" s="18">
         <v>33</v>
       </c>
-      <c r="C33" s="19">
+      <c r="C33" s="18">
         <v>14</v>
       </c>
-      <c r="D33" s="19" t="s">
+      <c r="D33" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E33" s="5" t="s">
@@ -3429,17 +3416,17 @@
       </c>
       <c r="J33" s="14"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="20">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" s="18">
         <v>15</v>
       </c>
-      <c r="B34" s="19">
+      <c r="B34" s="18">
         <v>27</v>
       </c>
-      <c r="C34" s="19">
+      <c r="C34" s="18">
         <v>15</v>
       </c>
-      <c r="D34" s="19" t="s">
+      <c r="D34" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E34" s="5" t="s">
@@ -3459,17 +3446,17 @@
       </c>
       <c r="J34" s="14"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="20">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A35" s="18">
         <v>7</v>
       </c>
-      <c r="B35" s="20">
+      <c r="B35" s="18">
         <v>23</v>
       </c>
-      <c r="C35" s="19">
+      <c r="C35" s="18">
         <v>16</v>
       </c>
-      <c r="D35" s="19" t="s">
+      <c r="D35" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E35" s="5" t="s">
@@ -3489,17 +3476,17 @@
       </c>
       <c r="J35" s="14"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="20">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A36" s="18">
         <v>12</v>
       </c>
-      <c r="B36" s="20">
+      <c r="B36" s="18">
         <v>18</v>
       </c>
-      <c r="C36" s="19">
+      <c r="C36" s="18">
         <v>17</v>
       </c>
-      <c r="D36" s="19" t="s">
+      <c r="D36" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E36" s="5" t="s">
@@ -3519,167 +3506,167 @@
       </c>
       <c r="J36" s="14"/>
     </row>
-    <row r="37" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="31">
+    <row r="37" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="27">
         <v>4</v>
       </c>
-      <c r="B37" s="35">
+      <c r="B37" s="30">
         <v>13</v>
       </c>
-      <c r="C37" s="32">
+      <c r="C37" s="27">
         <v>18</v>
       </c>
-      <c r="D37" s="32" t="s">
-        <v>402</v>
-      </c>
-      <c r="E37" s="33" t="s">
+      <c r="D37" s="27" t="s">
+        <v>402</v>
+      </c>
+      <c r="E37" s="28" t="s">
         <v>191</v>
       </c>
-      <c r="F37" s="33" t="s">
+      <c r="F37" s="28" t="s">
         <v>203</v>
       </c>
-      <c r="G37" s="33" t="s">
+      <c r="G37" s="28" t="s">
         <v>204</v>
       </c>
-      <c r="H37" s="34">
+      <c r="H37" s="29">
         <v>1878000</v>
       </c>
-      <c r="I37" s="33" t="s">
-        <v>407</v>
-      </c>
-      <c r="J37" s="34"/>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="28">
+      <c r="I37" s="28" t="s">
+        <v>407</v>
+      </c>
+      <c r="J37" s="29"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A38" s="24">
         <v>12</v>
       </c>
-      <c r="B38" s="28">
+      <c r="B38" s="24">
         <v>555</v>
       </c>
-      <c r="C38" s="28">
+      <c r="C38" s="24">
         <v>1</v>
       </c>
-      <c r="D38" s="28" t="s">
+      <c r="D38" s="24" t="s">
         <v>401</v>
       </c>
-      <c r="E38" s="29" t="s">
+      <c r="E38" s="25" t="s">
         <v>336</v>
       </c>
-      <c r="F38" s="29" t="s">
+      <c r="F38" s="25" t="s">
         <v>352</v>
       </c>
-      <c r="G38" s="29" t="s">
+      <c r="G38" s="25" t="s">
         <v>353</v>
       </c>
-      <c r="H38" s="44">
+      <c r="H38" s="38">
         <v>5000000</v>
       </c>
-      <c r="I38" s="29" t="s">
+      <c r="I38" s="25" t="s">
         <v>406</v>
       </c>
-      <c r="J38" s="30"/>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="17">
+      <c r="J38" s="26"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A39" s="16">
         <v>3</v>
       </c>
-      <c r="B39" s="17">
+      <c r="B39" s="16">
         <v>443</v>
       </c>
-      <c r="C39" s="17">
+      <c r="C39" s="16">
         <v>2</v>
       </c>
-      <c r="D39" s="17" t="s">
+      <c r="D39" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E39" s="18" t="s">
+      <c r="E39" s="17" t="s">
         <v>336</v>
       </c>
-      <c r="F39" s="18" t="s">
+      <c r="F39" s="17" t="s">
         <v>370</v>
       </c>
-      <c r="G39" s="18" t="s">
+      <c r="G39" s="17" t="s">
         <v>371</v>
       </c>
-      <c r="H39" s="43">
+      <c r="H39" s="37">
         <v>5000000</v>
       </c>
-      <c r="I39" s="18" t="s">
+      <c r="I39" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J39" s="14"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="17">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A40" s="16">
         <v>7</v>
       </c>
-      <c r="B40" s="17">
+      <c r="B40" s="16">
         <v>435</v>
       </c>
-      <c r="C40" s="17">
+      <c r="C40" s="16">
         <v>3</v>
       </c>
-      <c r="D40" s="17" t="s">
+      <c r="D40" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E40" s="18" t="s">
+      <c r="E40" s="17" t="s">
         <v>336</v>
       </c>
-      <c r="F40" s="18" t="s">
+      <c r="F40" s="17" t="s">
         <v>376</v>
       </c>
-      <c r="G40" s="18" t="s">
+      <c r="G40" s="17" t="s">
         <v>377</v>
       </c>
-      <c r="H40" s="43">
+      <c r="H40" s="37">
         <v>2384400</v>
       </c>
-      <c r="I40" s="18" t="s">
+      <c r="I40" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J40" s="14"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="17">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" s="16">
         <v>10</v>
       </c>
-      <c r="B41" s="17">
+      <c r="B41" s="16">
         <v>184</v>
       </c>
-      <c r="C41" s="17">
+      <c r="C41" s="16">
         <v>4</v>
       </c>
-      <c r="D41" s="17" t="s">
+      <c r="D41" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E41" s="18" t="s">
+      <c r="E41" s="17" t="s">
         <v>336</v>
       </c>
-      <c r="F41" s="18" t="s">
+      <c r="F41" s="17" t="s">
         <v>341</v>
       </c>
-      <c r="G41" s="18" t="s">
+      <c r="G41" s="17" t="s">
         <v>342</v>
       </c>
-      <c r="H41" s="43">
+      <c r="H41" s="37">
         <v>5000000</v>
       </c>
-      <c r="I41" s="18" t="s">
+      <c r="I41" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J41" s="14"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="20">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" s="18">
         <v>4</v>
       </c>
-      <c r="B42" s="20">
+      <c r="B42" s="18">
         <v>178</v>
       </c>
-      <c r="C42" s="19">
+      <c r="C42" s="18">
         <v>5</v>
       </c>
-      <c r="D42" s="19" t="s">
+      <c r="D42" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E42" s="5" t="s">
@@ -3699,17 +3686,17 @@
       </c>
       <c r="J42" s="14"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="20">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A43" s="18">
         <v>13</v>
       </c>
-      <c r="B43" s="20">
+      <c r="B43" s="18">
         <v>106</v>
       </c>
-      <c r="C43" s="19">
+      <c r="C43" s="18">
         <v>6</v>
       </c>
-      <c r="D43" s="19" t="s">
+      <c r="D43" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E43" s="5" t="s">
@@ -3729,59 +3716,59 @@
       </c>
       <c r="J43" s="14"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="17">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A44" s="16">
         <v>2</v>
       </c>
-      <c r="B44" s="17">
+      <c r="B44" s="16">
         <v>89</v>
       </c>
-      <c r="C44" s="17">
+      <c r="C44" s="16">
         <v>7</v>
       </c>
-      <c r="D44" s="17" t="s">
+      <c r="D44" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E44" s="18" t="s">
+      <c r="E44" s="17" t="s">
         <v>336</v>
       </c>
-      <c r="F44" s="18" t="s">
+      <c r="F44" s="17" t="s">
         <v>379</v>
       </c>
-      <c r="G44" s="18" t="s">
+      <c r="G44" s="17" t="s">
         <v>380</v>
       </c>
-      <c r="H44" s="43">
+      <c r="H44" s="37">
         <v>1300000</v>
       </c>
-      <c r="I44" s="18" t="s">
+      <c r="I44" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J44" s="14"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="19">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A45" s="18">
         <v>20</v>
       </c>
-      <c r="B45" s="19">
+      <c r="B45" s="18">
         <v>82</v>
       </c>
-      <c r="C45" s="19">
+      <c r="C45" s="18">
         <v>8</v>
       </c>
-      <c r="D45" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="E45" s="21" t="s">
+      <c r="D45" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="E45" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="F45" s="21" t="s">
+      <c r="F45" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="G45" s="21" t="s">
+      <c r="G45" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="H45" s="24">
+      <c r="H45" s="21">
         <v>3950000</v>
       </c>
       <c r="I45" s="5" t="s">
@@ -3789,17 +3776,17 @@
       </c>
       <c r="J45" s="14"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="20">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A46" s="18">
         <v>28</v>
       </c>
-      <c r="B46" s="19">
+      <c r="B46" s="18">
         <v>66</v>
       </c>
-      <c r="C46" s="19">
+      <c r="C46" s="18">
         <v>9</v>
       </c>
-      <c r="D46" s="19" t="s">
+      <c r="D46" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E46" s="5" t="s">
@@ -3819,47 +3806,47 @@
       </c>
       <c r="J46" s="14"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="17">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A47" s="16">
         <v>22</v>
       </c>
-      <c r="B47" s="17">
+      <c r="B47" s="16">
         <v>55</v>
       </c>
-      <c r="C47" s="17">
+      <c r="C47" s="16">
         <v>10</v>
       </c>
-      <c r="D47" s="17" t="s">
+      <c r="D47" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E47" s="18" t="s">
+      <c r="E47" s="17" t="s">
         <v>336</v>
       </c>
-      <c r="F47" s="18" t="s">
+      <c r="F47" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="G47" s="18" t="s">
+      <c r="G47" s="17" t="s">
         <v>338</v>
       </c>
-      <c r="H47" s="43">
+      <c r="H47" s="37">
         <v>813500</v>
       </c>
-      <c r="I47" s="18" t="s">
+      <c r="I47" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J47" s="14"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="20">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A48" s="18">
         <v>24</v>
       </c>
-      <c r="B48" s="19">
+      <c r="B48" s="18">
         <v>49</v>
       </c>
-      <c r="C48" s="19">
+      <c r="C48" s="18">
         <v>11</v>
       </c>
-      <c r="D48" s="19" t="s">
+      <c r="D48" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E48" s="5" t="s">
@@ -3879,47 +3866,47 @@
       </c>
       <c r="J48" s="14"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="17">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49" s="16">
         <v>9</v>
       </c>
-      <c r="B49" s="17">
+      <c r="B49" s="16">
         <v>45</v>
       </c>
-      <c r="C49" s="17">
+      <c r="C49" s="16">
         <v>12</v>
       </c>
-      <c r="D49" s="17" t="s">
+      <c r="D49" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E49" s="18" t="s">
+      <c r="E49" s="17" t="s">
         <v>336</v>
       </c>
-      <c r="F49" s="18" t="s">
+      <c r="F49" s="17" t="s">
         <v>350</v>
       </c>
-      <c r="G49" s="18" t="s">
+      <c r="G49" s="17" t="s">
         <v>351</v>
       </c>
-      <c r="H49" s="43">
+      <c r="H49" s="37">
         <v>357585</v>
       </c>
-      <c r="I49" s="18" t="s">
+      <c r="I49" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J49" s="14"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="20">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" s="18">
         <v>18</v>
       </c>
-      <c r="B50" s="19">
+      <c r="B50" s="18">
         <v>43</v>
       </c>
-      <c r="C50" s="19">
+      <c r="C50" s="18">
         <v>13</v>
       </c>
-      <c r="D50" s="19" t="s">
+      <c r="D50" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E50" s="5" t="s">
@@ -3939,80 +3926,80 @@
       </c>
       <c r="J50" s="14"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="17">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" s="16">
         <v>19</v>
       </c>
-      <c r="B51" s="17">
+      <c r="B51" s="16">
         <v>32</v>
       </c>
-      <c r="C51" s="17">
+      <c r="C51" s="16">
         <v>14</v>
       </c>
-      <c r="D51" s="17" t="s">
+      <c r="D51" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E51" s="18" t="s">
+      <c r="E51" s="17" t="s">
         <v>336</v>
       </c>
-      <c r="F51" s="18" t="s">
+      <c r="F51" s="17" t="s">
         <v>334</v>
       </c>
-      <c r="G51" s="18" t="s">
+      <c r="G51" s="17" t="s">
         <v>335</v>
       </c>
-      <c r="H51" s="43">
+      <c r="H51" s="37">
         <v>1340000</v>
       </c>
-      <c r="I51" s="18" t="s">
+      <c r="I51" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J51" s="14"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" s="17">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" s="16">
         <v>16</v>
       </c>
-      <c r="B52" s="17">
+      <c r="B52" s="16">
         <v>27</v>
       </c>
-      <c r="C52" s="17">
+      <c r="C52" s="16">
         <v>15</v>
       </c>
-      <c r="D52" s="17" t="s">
+      <c r="D52" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E52" s="18" t="s">
+      <c r="E52" s="17" t="s">
         <v>336</v>
       </c>
-      <c r="F52" s="18" t="s">
+      <c r="F52" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="G52" s="18" t="s">
+      <c r="G52" s="17" t="s">
         <v>388</v>
       </c>
-      <c r="H52" s="43">
+      <c r="H52" s="37">
         <v>732750</v>
       </c>
-      <c r="I52" s="18" t="s">
+      <c r="I52" s="17" t="s">
         <v>406</v>
       </c>
-      <c r="J52" s="22">
+      <c r="J52" s="19">
         <f>SUM(H38:H41,H44,H47,H49,H51:H52)</f>
         <v>21928235</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" s="20">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53" s="18">
         <v>17</v>
       </c>
-      <c r="B53" s="19">
+      <c r="B53" s="18">
         <v>24</v>
       </c>
-      <c r="C53" s="19">
+      <c r="C53" s="18">
         <v>16</v>
       </c>
-      <c r="D53" s="19" t="s">
+      <c r="D53" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E53" s="5" t="s">
@@ -4032,17 +4019,17 @@
       </c>
       <c r="J53" s="14"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="20">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54" s="18">
         <v>6</v>
       </c>
-      <c r="B54" s="19">
+      <c r="B54" s="18">
         <v>23</v>
       </c>
-      <c r="C54" s="19">
+      <c r="C54" s="18">
         <v>17</v>
       </c>
-      <c r="D54" s="19" t="s">
+      <c r="D54" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E54" s="5" t="s">
@@ -4062,17 +4049,17 @@
       </c>
       <c r="J54" s="14"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="20">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" s="18">
         <v>25</v>
       </c>
-      <c r="B55" s="19">
+      <c r="B55" s="18">
         <v>22</v>
       </c>
-      <c r="C55" s="19">
+      <c r="C55" s="18">
         <v>18</v>
       </c>
-      <c r="D55" s="19" t="s">
+      <c r="D55" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E55" s="5" t="s">
@@ -4092,17 +4079,17 @@
       </c>
       <c r="J55" s="14"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="20">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56" s="18">
         <v>5</v>
       </c>
-      <c r="B56" s="19">
+      <c r="B56" s="18">
         <v>20</v>
       </c>
-      <c r="C56" s="19">
+      <c r="C56" s="18">
         <v>19</v>
       </c>
-      <c r="D56" s="19" t="s">
+      <c r="D56" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E56" s="5" t="s">
@@ -4122,17 +4109,17 @@
       </c>
       <c r="J56" s="14"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="20">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" s="18">
         <v>1</v>
       </c>
-      <c r="B57" s="19">
+      <c r="B57" s="18">
         <v>20</v>
       </c>
-      <c r="C57" s="19">
+      <c r="C57" s="18">
         <v>20</v>
       </c>
-      <c r="D57" s="19" t="s">
+      <c r="D57" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E57" s="5" t="s">
@@ -4152,17 +4139,17 @@
       </c>
       <c r="J57" s="14"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="20">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" s="18">
         <v>26</v>
       </c>
-      <c r="B58" s="19">
+      <c r="B58" s="18">
         <v>19</v>
       </c>
-      <c r="C58" s="19">
+      <c r="C58" s="18">
         <v>21</v>
       </c>
-      <c r="D58" s="19" t="s">
+      <c r="D58" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E58" s="5" t="s">
@@ -4182,17 +4169,17 @@
       </c>
       <c r="J58" s="14"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="20">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59" s="18">
         <v>14</v>
       </c>
-      <c r="B59" s="19">
+      <c r="B59" s="18">
         <v>17</v>
       </c>
-      <c r="C59" s="19">
+      <c r="C59" s="18">
         <v>22</v>
       </c>
-      <c r="D59" s="19" t="s">
+      <c r="D59" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E59" s="5" t="s">
@@ -4212,47 +4199,47 @@
       </c>
       <c r="J59" s="14"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="19">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" s="18">
         <v>23</v>
       </c>
-      <c r="B60" s="19">
+      <c r="B60" s="18">
         <v>16</v>
       </c>
-      <c r="C60" s="19">
+      <c r="C60" s="18">
         <v>23</v>
       </c>
-      <c r="D60" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="E60" s="21" t="s">
+      <c r="D60" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="E60" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="F60" s="21" t="s">
+      <c r="F60" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="G60" s="21" t="s">
+      <c r="G60" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="H60" s="24">
+      <c r="H60" s="21">
         <v>145000</v>
       </c>
       <c r="I60" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="J60" s="24"/>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="20">
+      <c r="J60" s="21"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A61" s="18">
         <v>21</v>
       </c>
-      <c r="B61" s="20">
+      <c r="B61" s="18">
         <v>13</v>
       </c>
-      <c r="C61" s="19">
+      <c r="C61" s="18">
         <v>24</v>
       </c>
-      <c r="D61" s="19" t="s">
+      <c r="D61" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E61" s="5" t="s">
@@ -4272,17 +4259,17 @@
       </c>
       <c r="J61" s="14"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="20">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62" s="18">
         <v>29</v>
       </c>
-      <c r="B62" s="20">
+      <c r="B62" s="18">
         <v>12</v>
       </c>
-      <c r="C62" s="19">
+      <c r="C62" s="18">
         <v>25</v>
       </c>
-      <c r="D62" s="19" t="s">
+      <c r="D62" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E62" s="5" t="s">
@@ -4302,17 +4289,17 @@
       </c>
       <c r="J62" s="14"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="20">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A63" s="18">
         <v>8</v>
       </c>
-      <c r="B63" s="20">
+      <c r="B63" s="18">
         <v>7</v>
       </c>
-      <c r="C63" s="19">
+      <c r="C63" s="18">
         <v>26</v>
       </c>
-      <c r="D63" s="19" t="s">
+      <c r="D63" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E63" s="5" t="s">
@@ -4332,17 +4319,17 @@
       </c>
       <c r="J63" s="14"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="20">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A64" s="18">
         <v>27</v>
       </c>
-      <c r="B64" s="20">
+      <c r="B64" s="18">
         <v>7</v>
       </c>
-      <c r="C64" s="19">
+      <c r="C64" s="18">
         <v>27</v>
       </c>
-      <c r="D64" s="19" t="s">
+      <c r="D64" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E64" s="5" t="s">
@@ -4362,17 +4349,17 @@
       </c>
       <c r="J64" s="14"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" s="20">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A65" s="18">
         <v>11</v>
       </c>
-      <c r="B65" s="20">
+      <c r="B65" s="18">
         <v>6</v>
       </c>
-      <c r="C65" s="19">
+      <c r="C65" s="18">
         <v>28</v>
       </c>
-      <c r="D65" s="19" t="s">
+      <c r="D65" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E65" s="5" t="s">
@@ -4392,17 +4379,17 @@
       </c>
       <c r="J65" s="14"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="20">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A66" s="18">
         <v>30</v>
       </c>
-      <c r="B66" s="20">
+      <c r="B66" s="18">
         <v>6</v>
       </c>
-      <c r="C66" s="19">
+      <c r="C66" s="18">
         <v>29</v>
       </c>
-      <c r="D66" s="19" t="s">
+      <c r="D66" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E66" s="5" t="s">
@@ -4422,227 +4409,227 @@
       </c>
       <c r="J66" s="14"/>
     </row>
-    <row r="67" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="31">
+    <row r="67" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="27">
         <v>15</v>
       </c>
-      <c r="B67" s="32">
+      <c r="B67" s="27">
         <v>2</v>
       </c>
-      <c r="C67" s="32">
+      <c r="C67" s="27">
         <v>30</v>
       </c>
-      <c r="D67" s="32" t="s">
-        <v>402</v>
-      </c>
-      <c r="E67" s="33" t="s">
+      <c r="D67" s="27" t="s">
+        <v>402</v>
+      </c>
+      <c r="E67" s="28" t="s">
         <v>336</v>
       </c>
-      <c r="F67" s="33" t="s">
+      <c r="F67" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="G67" s="33" t="s">
+      <c r="G67" s="28" t="s">
         <v>344</v>
       </c>
-      <c r="H67" s="34">
+      <c r="H67" s="29">
         <v>315000</v>
       </c>
-      <c r="I67" s="33" t="s">
-        <v>407</v>
-      </c>
-      <c r="J67" s="34"/>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" s="28">
+      <c r="I67" s="28" t="s">
+        <v>407</v>
+      </c>
+      <c r="J67" s="29"/>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A68" s="24">
         <v>9</v>
       </c>
-      <c r="B68" s="28">
+      <c r="B68" s="24">
         <v>318</v>
       </c>
-      <c r="C68" s="28">
+      <c r="C68" s="24">
         <v>1</v>
       </c>
-      <c r="D68" s="28" t="s">
+      <c r="D68" s="24" t="s">
         <v>401</v>
       </c>
-      <c r="E68" s="29" t="s">
+      <c r="E68" s="25" t="s">
         <v>165</v>
       </c>
-      <c r="F68" s="29" t="s">
+      <c r="F68" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="G68" s="29" t="s">
+      <c r="G68" s="25" t="s">
         <v>170</v>
       </c>
-      <c r="H68" s="44">
+      <c r="H68" s="38">
         <v>5000000</v>
       </c>
-      <c r="I68" s="29" t="s">
+      <c r="I68" s="25" t="s">
         <v>406</v>
       </c>
-      <c r="J68" s="30"/>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" s="17">
+      <c r="J68" s="26"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A69" s="16">
         <v>7</v>
       </c>
-      <c r="B69" s="17">
+      <c r="B69" s="16">
         <v>118</v>
       </c>
-      <c r="C69" s="17">
+      <c r="C69" s="16">
         <v>2</v>
       </c>
-      <c r="D69" s="17" t="s">
+      <c r="D69" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E69" s="18" t="s">
+      <c r="E69" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="F69" s="18" t="s">
+      <c r="F69" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="G69" s="18" t="s">
+      <c r="G69" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="H69" s="43">
+      <c r="H69" s="37">
         <v>2400000</v>
       </c>
-      <c r="I69" s="18" t="s">
+      <c r="I69" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J69" s="14"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" s="17">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A70" s="16">
         <v>10</v>
       </c>
-      <c r="B70" s="17">
+      <c r="B70" s="16">
         <v>112</v>
       </c>
-      <c r="C70" s="17">
+      <c r="C70" s="16">
         <v>3</v>
       </c>
-      <c r="D70" s="17" t="s">
+      <c r="D70" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E70" s="18" t="s">
+      <c r="E70" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="F70" s="18" t="s">
+      <c r="F70" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="G70" s="18" t="s">
+      <c r="G70" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="H70" s="43">
+      <c r="H70" s="37">
         <v>1613000</v>
       </c>
-      <c r="I70" s="18" t="s">
+      <c r="I70" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J70" s="14"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A71" s="17">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A71" s="16">
         <v>4</v>
       </c>
-      <c r="B71" s="17">
+      <c r="B71" s="16">
         <v>110</v>
       </c>
-      <c r="C71" s="17">
+      <c r="C71" s="16">
         <v>4</v>
       </c>
-      <c r="D71" s="17" t="s">
+      <c r="D71" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E71" s="18" t="s">
+      <c r="E71" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="F71" s="18" t="s">
+      <c r="F71" s="17" t="s">
         <v>181</v>
       </c>
-      <c r="G71" s="18" t="s">
+      <c r="G71" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="H71" s="43">
+      <c r="H71" s="37">
         <v>1947000</v>
       </c>
-      <c r="I71" s="18" t="s">
+      <c r="I71" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J71" s="14"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A72" s="17">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A72" s="16">
         <v>8</v>
       </c>
-      <c r="B72" s="17">
+      <c r="B72" s="16">
         <v>64</v>
       </c>
-      <c r="C72" s="17">
+      <c r="C72" s="16">
         <v>5</v>
       </c>
-      <c r="D72" s="17" t="s">
+      <c r="D72" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E72" s="18" t="s">
+      <c r="E72" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="F72" s="18" t="s">
+      <c r="F72" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="G72" s="18" t="s">
+      <c r="G72" s="17" t="s">
         <v>188</v>
       </c>
-      <c r="H72" s="43">
+      <c r="H72" s="37">
         <v>2200000</v>
       </c>
-      <c r="I72" s="18" t="s">
+      <c r="I72" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J72" s="14"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A73" s="17">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A73" s="16">
         <v>13</v>
       </c>
-      <c r="B73" s="17">
+      <c r="B73" s="16">
         <v>47</v>
       </c>
-      <c r="C73" s="17">
+      <c r="C73" s="16">
         <v>6</v>
       </c>
-      <c r="D73" s="17" t="s">
+      <c r="D73" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E73" s="18" t="s">
+      <c r="E73" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="F73" s="18" t="s">
+      <c r="F73" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="G73" s="18" t="s">
+      <c r="G73" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="H73" s="43">
+      <c r="H73" s="37">
         <v>5000000</v>
       </c>
-      <c r="I73" s="18" t="s">
+      <c r="I73" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J73" s="14"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" s="20">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A74" s="18">
         <v>14</v>
       </c>
-      <c r="B74" s="20">
+      <c r="B74" s="18">
         <v>27</v>
       </c>
-      <c r="C74" s="19">
+      <c r="C74" s="18">
         <v>7</v>
       </c>
-      <c r="D74" s="19" t="s">
+      <c r="D74" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E74" s="5" t="s">
@@ -4662,17 +4649,17 @@
       </c>
       <c r="J74" s="14"/>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A75" s="20">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A75" s="18">
         <v>6</v>
       </c>
-      <c r="B75" s="20">
+      <c r="B75" s="18">
         <v>20</v>
       </c>
-      <c r="C75" s="19">
+      <c r="C75" s="18">
         <v>8</v>
       </c>
-      <c r="D75" s="19" t="s">
+      <c r="D75" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E75" s="5" t="s">
@@ -4692,17 +4679,17 @@
       </c>
       <c r="J75" s="14"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A76" s="20">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A76" s="18">
         <v>12</v>
       </c>
-      <c r="B76" s="20">
+      <c r="B76" s="18">
         <v>12</v>
       </c>
-      <c r="C76" s="19">
+      <c r="C76" s="18">
         <v>9</v>
       </c>
-      <c r="D76" s="19" t="s">
+      <c r="D76" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E76" s="5" t="s">
@@ -4722,17 +4709,17 @@
       </c>
       <c r="J76" s="14"/>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" s="20">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A77" s="18">
         <v>5</v>
       </c>
-      <c r="B77" s="20">
+      <c r="B77" s="18">
         <v>11</v>
       </c>
-      <c r="C77" s="19">
+      <c r="C77" s="18">
         <v>10</v>
       </c>
-      <c r="D77" s="19" t="s">
+      <c r="D77" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E77" s="5" t="s">
@@ -4752,17 +4739,17 @@
       </c>
       <c r="J77" s="14"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A78" s="20">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A78" s="18">
         <v>11</v>
       </c>
-      <c r="B78" s="23">
+      <c r="B78" s="20">
         <v>7</v>
       </c>
-      <c r="C78" s="19">
+      <c r="C78" s="18">
         <v>11</v>
       </c>
-      <c r="D78" s="19" t="s">
+      <c r="D78" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E78" s="5" t="s">
@@ -4782,50 +4769,50 @@
       </c>
       <c r="J78" s="14"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A79" s="17">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A79" s="16">
         <v>2</v>
       </c>
-      <c r="B79" s="25">
+      <c r="B79" s="22">
         <v>5</v>
       </c>
-      <c r="C79" s="17">
+      <c r="C79" s="16">
         <v>12</v>
       </c>
-      <c r="D79" s="17" t="s">
+      <c r="D79" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E79" s="18" t="s">
+      <c r="E79" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="F79" s="18" t="s">
+      <c r="F79" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="G79" s="18" t="s">
+      <c r="G79" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="H79" s="43">
+      <c r="H79" s="37">
         <v>250000</v>
       </c>
-      <c r="I79" s="18" t="s">
+      <c r="I79" s="17" t="s">
         <v>406</v>
       </c>
-      <c r="J79" s="22">
+      <c r="J79" s="19">
         <f>SUM(H68:H73,H79)</f>
         <v>18410000</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A80" s="20">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A80" s="18">
         <v>3</v>
       </c>
-      <c r="B80" s="23">
+      <c r="B80" s="20">
         <v>5</v>
       </c>
-      <c r="C80" s="19">
+      <c r="C80" s="18">
         <v>13</v>
       </c>
-      <c r="D80" s="19" t="s">
+      <c r="D80" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E80" s="5" t="s">
@@ -4845,239 +4832,239 @@
       </c>
       <c r="J80" s="14"/>
     </row>
-    <row r="81" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="31">
+    <row r="81" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="27">
         <v>1</v>
       </c>
-      <c r="B81" s="35">
+      <c r="B81" s="30">
         <v>5</v>
       </c>
-      <c r="C81" s="32">
+      <c r="C81" s="27">
         <v>14</v>
       </c>
-      <c r="D81" s="32" t="s">
-        <v>402</v>
-      </c>
-      <c r="E81" s="33" t="s">
+      <c r="D81" s="27" t="s">
+        <v>402</v>
+      </c>
+      <c r="E81" s="28" t="s">
         <v>165</v>
       </c>
-      <c r="F81" s="33" t="s">
+      <c r="F81" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="G81" s="33" t="s">
+      <c r="G81" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="H81" s="34">
+      <c r="H81" s="29">
         <v>300000</v>
       </c>
-      <c r="I81" s="33" t="s">
-        <v>407</v>
-      </c>
-      <c r="J81" s="34"/>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A82" s="28">
+      <c r="I81" s="28" t="s">
+        <v>407</v>
+      </c>
+      <c r="J81" s="29"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A82" s="24">
         <v>27</v>
       </c>
-      <c r="B82" s="28">
+      <c r="B82" s="24">
         <v>262</v>
       </c>
-      <c r="C82" s="28">
+      <c r="C82" s="24">
         <v>1</v>
       </c>
-      <c r="D82" s="28" t="s">
+      <c r="D82" s="24" t="s">
         <v>401</v>
       </c>
-      <c r="E82" s="29" t="s">
+      <c r="E82" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="F82" s="29" t="s">
+      <c r="F82" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="G82" s="29" t="s">
+      <c r="G82" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="H82" s="44">
+      <c r="H82" s="38">
         <v>1650000</v>
       </c>
-      <c r="I82" s="29" t="s">
+      <c r="I82" s="25" t="s">
         <v>406</v>
       </c>
-      <c r="J82" s="30"/>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A83" s="17">
+      <c r="J82" s="26"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A83" s="16">
         <v>4</v>
       </c>
-      <c r="B83" s="17">
+      <c r="B83" s="16">
         <v>256</v>
       </c>
-      <c r="C83" s="17">
+      <c r="C83" s="16">
         <v>2</v>
       </c>
-      <c r="D83" s="17" t="s">
+      <c r="D83" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E83" s="18" t="s">
+      <c r="E83" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="F83" s="18" t="s">
+      <c r="F83" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="G83" s="18" t="s">
+      <c r="G83" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="H83" s="43">
+      <c r="H83" s="37">
         <v>5000000</v>
       </c>
-      <c r="I83" s="18" t="s">
+      <c r="I83" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J83" s="14"/>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A84" s="17">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A84" s="16">
         <v>1</v>
       </c>
-      <c r="B84" s="17">
+      <c r="B84" s="16">
         <v>191</v>
       </c>
-      <c r="C84" s="17">
+      <c r="C84" s="16">
         <v>3</v>
       </c>
-      <c r="D84" s="17" t="s">
+      <c r="D84" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E84" s="18" t="s">
+      <c r="E84" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="F84" s="18" t="s">
+      <c r="F84" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="G84" s="18" t="s">
+      <c r="G84" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="H84" s="43">
+      <c r="H84" s="37">
         <v>5000000</v>
       </c>
-      <c r="I84" s="18" t="s">
+      <c r="I84" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J84" s="14"/>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A85" s="17">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A85" s="16">
         <v>29</v>
       </c>
-      <c r="B85" s="17">
+      <c r="B85" s="16">
         <v>175</v>
       </c>
-      <c r="C85" s="17">
+      <c r="C85" s="16">
         <v>4</v>
       </c>
-      <c r="D85" s="17" t="s">
+      <c r="D85" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E85" s="18" t="s">
+      <c r="E85" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="F85" s="18" t="s">
+      <c r="F85" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="G85" s="18" t="s">
+      <c r="G85" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="H85" s="43">
+      <c r="H85" s="37">
         <v>5000000</v>
       </c>
-      <c r="I85" s="18" t="s">
+      <c r="I85" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J85" s="14"/>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A86" s="17">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A86" s="16">
         <v>37</v>
       </c>
-      <c r="B86" s="17">
+      <c r="B86" s="16">
         <v>160</v>
       </c>
-      <c r="C86" s="17">
+      <c r="C86" s="16">
         <v>5</v>
       </c>
-      <c r="D86" s="17" t="s">
+      <c r="D86" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E86" s="18" t="s">
+      <c r="E86" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="F86" s="18" t="s">
+      <c r="F86" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="G86" s="18" t="s">
+      <c r="G86" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="H86" s="43">
+      <c r="H86" s="37">
         <v>450000</v>
       </c>
-      <c r="I86" s="18" t="s">
+      <c r="I86" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J86" s="14"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A87" s="17">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A87" s="16">
         <v>2</v>
       </c>
-      <c r="B87" s="17">
+      <c r="B87" s="16">
         <v>123</v>
       </c>
-      <c r="C87" s="17">
+      <c r="C87" s="16">
         <v>6</v>
       </c>
-      <c r="D87" s="17" t="s">
+      <c r="D87" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E87" s="18" t="s">
+      <c r="E87" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="F87" s="18" t="s">
+      <c r="F87" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="G87" s="18" t="s">
+      <c r="G87" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="H87" s="43">
+      <c r="H87" s="37">
         <v>5000000</v>
       </c>
-      <c r="I87" s="18" t="s">
+      <c r="I87" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J87" s="14"/>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A88" s="19">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A88" s="18">
         <v>38</v>
       </c>
-      <c r="B88" s="20">
+      <c r="B88" s="18">
         <v>97</v>
       </c>
-      <c r="C88" s="19">
+      <c r="C88" s="18">
         <v>7</v>
       </c>
-      <c r="D88" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="E88" s="21" t="s">
+      <c r="D88" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="E88" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F88" s="21" t="s">
+      <c r="F88" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G88" s="21" t="s">
+      <c r="G88" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="H88" s="24">
+      <c r="H88" s="21">
         <v>4227000</v>
       </c>
       <c r="I88" s="5" t="s">
@@ -5085,77 +5072,77 @@
       </c>
       <c r="J88" s="14"/>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A89" s="17">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A89" s="16">
         <v>24</v>
       </c>
-      <c r="B89" s="17">
+      <c r="B89" s="16">
         <v>83</v>
       </c>
-      <c r="C89" s="17">
+      <c r="C89" s="16">
         <v>8</v>
       </c>
-      <c r="D89" s="17" t="s">
+      <c r="D89" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E89" s="18" t="s">
+      <c r="E89" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="F89" s="18" t="s">
+      <c r="F89" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="G89" s="18" t="s">
+      <c r="G89" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="H89" s="43">
+      <c r="H89" s="37">
         <v>3373000</v>
       </c>
-      <c r="I89" s="18" t="s">
+      <c r="I89" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J89" s="14"/>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A90" s="17">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A90" s="16">
         <v>16</v>
       </c>
-      <c r="B90" s="17">
+      <c r="B90" s="16">
         <v>63</v>
       </c>
-      <c r="C90" s="17">
+      <c r="C90" s="16">
         <v>9</v>
       </c>
-      <c r="D90" s="17" t="s">
+      <c r="D90" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E90" s="18" t="s">
+      <c r="E90" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="F90" s="18" t="s">
+      <c r="F90" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="G90" s="18" t="s">
+      <c r="G90" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="H90" s="43">
+      <c r="H90" s="37">
         <v>577950</v>
       </c>
-      <c r="I90" s="18" t="s">
+      <c r="I90" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J90" s="14"/>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A91" s="20">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A91" s="18">
         <v>23</v>
       </c>
-      <c r="B91" s="20">
+      <c r="B91" s="18">
         <v>61</v>
       </c>
-      <c r="C91" s="19">
+      <c r="C91" s="18">
         <v>10</v>
       </c>
-      <c r="D91" s="19" t="s">
+      <c r="D91" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E91" s="5" t="s">
@@ -5175,17 +5162,17 @@
       </c>
       <c r="J91" s="14"/>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A92" s="20">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A92" s="18">
         <v>31</v>
       </c>
-      <c r="B92" s="20">
+      <c r="B92" s="18">
         <v>51</v>
       </c>
-      <c r="C92" s="19">
+      <c r="C92" s="18">
         <v>11</v>
       </c>
-      <c r="D92" s="19" t="s">
+      <c r="D92" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E92" s="5" t="s">
@@ -5205,17 +5192,17 @@
       </c>
       <c r="J92" s="14"/>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A93" s="20">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A93" s="18">
         <v>30</v>
       </c>
-      <c r="B93" s="20">
+      <c r="B93" s="18">
         <v>48</v>
       </c>
-      <c r="C93" s="19">
+      <c r="C93" s="18">
         <v>12</v>
       </c>
-      <c r="D93" s="19" t="s">
+      <c r="D93" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E93" s="5" t="s">
@@ -5235,17 +5222,17 @@
       </c>
       <c r="J93" s="14"/>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A94" s="20">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A94" s="18">
         <v>26</v>
       </c>
-      <c r="B94" s="19">
+      <c r="B94" s="18">
         <v>42</v>
       </c>
-      <c r="C94" s="19">
+      <c r="C94" s="18">
         <v>13</v>
       </c>
-      <c r="D94" s="19" t="s">
+      <c r="D94" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E94" s="5" t="s">
@@ -5265,17 +5252,17 @@
       </c>
       <c r="J94" s="14"/>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A95" s="20">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A95" s="18">
         <v>17</v>
       </c>
-      <c r="B95" s="19">
+      <c r="B95" s="18">
         <v>40</v>
       </c>
-      <c r="C95" s="19">
+      <c r="C95" s="18">
         <v>14</v>
       </c>
-      <c r="D95" s="19" t="s">
+      <c r="D95" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E95" s="5" t="s">
@@ -5295,17 +5282,17 @@
       </c>
       <c r="J95" s="14"/>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A96" s="20">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A96" s="18">
         <v>20</v>
       </c>
-      <c r="B96" s="19">
+      <c r="B96" s="18">
         <v>40</v>
       </c>
-      <c r="C96" s="19">
+      <c r="C96" s="18">
         <v>15</v>
       </c>
-      <c r="D96" s="19" t="s">
+      <c r="D96" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E96" s="5" t="s">
@@ -5325,17 +5312,17 @@
       </c>
       <c r="J96" s="14"/>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A97" s="20">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A97" s="18">
         <v>39</v>
       </c>
-      <c r="B97" s="19">
+      <c r="B97" s="18">
         <v>28</v>
       </c>
-      <c r="C97" s="19">
+      <c r="C97" s="18">
         <v>16</v>
       </c>
-      <c r="D97" s="19" t="s">
+      <c r="D97" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E97" s="5" t="s">
@@ -5355,17 +5342,17 @@
       </c>
       <c r="J97" s="14"/>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A98" s="20">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A98" s="18">
         <v>6</v>
       </c>
-      <c r="B98" s="19">
+      <c r="B98" s="18">
         <v>23</v>
       </c>
-      <c r="C98" s="19">
+      <c r="C98" s="18">
         <v>17</v>
       </c>
-      <c r="D98" s="19" t="s">
+      <c r="D98" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E98" s="5" t="s">
@@ -5385,17 +5372,17 @@
       </c>
       <c r="J98" s="14"/>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A99" s="20">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A99" s="18">
         <v>15</v>
       </c>
-      <c r="B99" s="19">
+      <c r="B99" s="18">
         <v>22</v>
       </c>
-      <c r="C99" s="19">
+      <c r="C99" s="18">
         <v>18</v>
       </c>
-      <c r="D99" s="19" t="s">
+      <c r="D99" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E99" s="5" t="s">
@@ -5415,47 +5402,47 @@
       </c>
       <c r="J99" s="14"/>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A100" s="17">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A100" s="16">
         <v>13</v>
       </c>
-      <c r="B100" s="17">
+      <c r="B100" s="16">
         <v>22</v>
       </c>
-      <c r="C100" s="17">
+      <c r="C100" s="16">
         <v>19</v>
       </c>
-      <c r="D100" s="17" t="s">
+      <c r="D100" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E100" s="18" t="s">
+      <c r="E100" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="F100" s="18" t="s">
+      <c r="F100" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="G100" s="18" t="s">
+      <c r="G100" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="H100" s="43">
+      <c r="H100" s="37">
         <v>30000</v>
       </c>
-      <c r="I100" s="18" t="s">
+      <c r="I100" s="17" t="s">
         <v>406</v>
       </c>
-      <c r="J100" s="24"/>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A101" s="20">
+      <c r="J100" s="21"/>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A101" s="18">
         <v>35</v>
       </c>
-      <c r="B101" s="20">
+      <c r="B101" s="18">
         <v>21</v>
       </c>
-      <c r="C101" s="19">
+      <c r="C101" s="18">
         <v>20</v>
       </c>
-      <c r="D101" s="19" t="s">
+      <c r="D101" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E101" s="5" t="s">
@@ -5475,17 +5462,17 @@
       </c>
       <c r="J101" s="14"/>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A102" s="20">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A102" s="18">
         <v>14</v>
       </c>
-      <c r="B102" s="20">
+      <c r="B102" s="18">
         <v>17</v>
       </c>
-      <c r="C102" s="19">
+      <c r="C102" s="18">
         <v>21</v>
       </c>
-      <c r="D102" s="19" t="s">
+      <c r="D102" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E102" s="5" t="s">
@@ -5505,17 +5492,17 @@
       </c>
       <c r="J102" s="14"/>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A103" s="20">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A103" s="18">
         <v>28</v>
       </c>
-      <c r="B103" s="20">
+      <c r="B103" s="18">
         <v>16</v>
       </c>
-      <c r="C103" s="19">
+      <c r="C103" s="18">
         <v>22</v>
       </c>
-      <c r="D103" s="19" t="s">
+      <c r="D103" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E103" s="5" t="s">
@@ -5535,17 +5522,17 @@
       </c>
       <c r="J103" s="14"/>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A104" s="20">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A104" s="18">
         <v>33</v>
       </c>
-      <c r="B104" s="20">
+      <c r="B104" s="18">
         <v>15</v>
       </c>
-      <c r="C104" s="19">
+      <c r="C104" s="18">
         <v>23</v>
       </c>
-      <c r="D104" s="19" t="s">
+      <c r="D104" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E104" s="5" t="s">
@@ -5565,17 +5552,17 @@
       </c>
       <c r="J104" s="14"/>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A105" s="20">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A105" s="18">
         <v>25</v>
       </c>
-      <c r="B105" s="20">
+      <c r="B105" s="18">
         <v>15</v>
       </c>
-      <c r="C105" s="19">
+      <c r="C105" s="18">
         <v>24</v>
       </c>
-      <c r="D105" s="19" t="s">
+      <c r="D105" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E105" s="5" t="s">
@@ -5595,47 +5582,47 @@
       </c>
       <c r="J105" s="14"/>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A106" s="19">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A106" s="18">
         <v>3</v>
       </c>
-      <c r="B106" s="20">
+      <c r="B106" s="18">
         <v>12</v>
       </c>
-      <c r="C106" s="19">
+      <c r="C106" s="18">
         <v>25</v>
       </c>
-      <c r="D106" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="E106" s="21" t="s">
+      <c r="D106" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="E106" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F106" s="21" t="s">
+      <c r="F106" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G106" s="21" t="s">
+      <c r="G106" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="H106" s="24">
+      <c r="H106" s="21">
         <v>465300</v>
       </c>
       <c r="I106" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="J106" s="26"/>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A107" s="20">
+      <c r="J106" s="23"/>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A107" s="18">
         <v>40</v>
       </c>
-      <c r="B107" s="20">
+      <c r="B107" s="18">
         <v>11</v>
       </c>
-      <c r="C107" s="19">
+      <c r="C107" s="18">
         <v>26</v>
       </c>
-      <c r="D107" s="19" t="s">
+      <c r="D107" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E107" s="5" t="s">
@@ -5655,50 +5642,50 @@
       </c>
       <c r="J107" s="14"/>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A108" s="17">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A108" s="16">
         <v>7</v>
       </c>
-      <c r="B108" s="25">
+      <c r="B108" s="22">
         <v>11</v>
       </c>
-      <c r="C108" s="17">
+      <c r="C108" s="16">
         <v>27</v>
       </c>
-      <c r="D108" s="17" t="s">
+      <c r="D108" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E108" s="18" t="s">
+      <c r="E108" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="F108" s="18" t="s">
+      <c r="F108" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="G108" s="18" t="s">
+      <c r="G108" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="H108" s="43">
+      <c r="H108" s="37">
         <v>120000</v>
       </c>
-      <c r="I108" s="18" t="s">
+      <c r="I108" s="17" t="s">
         <v>406</v>
       </c>
-      <c r="J108" s="22">
+      <c r="J108" s="19">
         <f>SUM(H82:H87,H89,H90,H100,H108)</f>
         <v>26200950</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A109" s="20">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A109" s="18">
         <v>34</v>
       </c>
-      <c r="B109" s="23">
+      <c r="B109" s="20">
         <v>10</v>
       </c>
-      <c r="C109" s="19">
+      <c r="C109" s="18">
         <v>28</v>
       </c>
-      <c r="D109" s="19" t="s">
+      <c r="D109" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E109" s="5" t="s">
@@ -5718,17 +5705,17 @@
       </c>
       <c r="J109" s="14"/>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A110" s="20">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A110" s="18">
         <v>10</v>
       </c>
-      <c r="B110" s="23">
+      <c r="B110" s="20">
         <v>9</v>
       </c>
-      <c r="C110" s="19">
+      <c r="C110" s="18">
         <v>29</v>
       </c>
-      <c r="D110" s="19" t="s">
+      <c r="D110" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E110" s="5" t="s">
@@ -5748,17 +5735,17 @@
       </c>
       <c r="J110" s="14"/>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A111" s="20">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A111" s="18">
         <v>8</v>
       </c>
-      <c r="B111" s="23">
+      <c r="B111" s="20">
         <v>9</v>
       </c>
-      <c r="C111" s="19">
+      <c r="C111" s="18">
         <v>30</v>
       </c>
-      <c r="D111" s="19" t="s">
+      <c r="D111" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E111" s="5" t="s">
@@ -5778,17 +5765,17 @@
       </c>
       <c r="J111" s="14"/>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A112" s="20">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A112" s="18">
         <v>11</v>
       </c>
-      <c r="B112" s="23">
+      <c r="B112" s="20">
         <v>8</v>
       </c>
-      <c r="C112" s="19">
+      <c r="C112" s="18">
         <v>31</v>
       </c>
-      <c r="D112" s="19" t="s">
+      <c r="D112" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E112" s="5" t="s">
@@ -5808,17 +5795,17 @@
       </c>
       <c r="J112" s="14"/>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A113" s="20">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A113" s="18">
         <v>12</v>
       </c>
-      <c r="B113" s="23">
+      <c r="B113" s="20">
         <v>8</v>
       </c>
-      <c r="C113" s="19">
+      <c r="C113" s="18">
         <v>32</v>
       </c>
-      <c r="D113" s="19" t="s">
+      <c r="D113" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E113" s="5" t="s">
@@ -5838,17 +5825,17 @@
       </c>
       <c r="J113" s="14"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A114" s="20">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A114" s="18">
         <v>9</v>
       </c>
-      <c r="B114" s="23">
+      <c r="B114" s="20">
         <v>7</v>
       </c>
-      <c r="C114" s="19">
+      <c r="C114" s="18">
         <v>33</v>
       </c>
-      <c r="D114" s="19" t="s">
+      <c r="D114" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E114" s="5" t="s">
@@ -5868,17 +5855,17 @@
       </c>
       <c r="J114" s="14"/>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A115" s="20">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A115" s="18">
         <v>5</v>
       </c>
-      <c r="B115" s="23">
+      <c r="B115" s="20">
         <v>7</v>
       </c>
-      <c r="C115" s="19">
+      <c r="C115" s="18">
         <v>34</v>
       </c>
-      <c r="D115" s="19" t="s">
+      <c r="D115" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E115" s="5" t="s">
@@ -5898,17 +5885,17 @@
       </c>
       <c r="J115" s="14"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A116" s="20">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A116" s="18">
         <v>22</v>
       </c>
-      <c r="B116" s="23">
+      <c r="B116" s="20">
         <v>7</v>
       </c>
-      <c r="C116" s="19">
+      <c r="C116" s="18">
         <v>35</v>
       </c>
-      <c r="D116" s="19" t="s">
+      <c r="D116" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E116" s="5" t="s">
@@ -5928,17 +5915,17 @@
       </c>
       <c r="J116" s="14"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A117" s="20">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A117" s="18">
         <v>36</v>
       </c>
-      <c r="B117" s="23">
+      <c r="B117" s="20">
         <v>7</v>
       </c>
-      <c r="C117" s="19">
+      <c r="C117" s="18">
         <v>36</v>
       </c>
-      <c r="D117" s="19" t="s">
+      <c r="D117" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E117" s="5" t="s">
@@ -5958,17 +5945,17 @@
       </c>
       <c r="J117" s="14"/>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A118" s="20">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A118" s="18">
         <v>19</v>
       </c>
-      <c r="B118" s="23">
+      <c r="B118" s="20">
         <v>6</v>
       </c>
-      <c r="C118" s="19">
+      <c r="C118" s="18">
         <v>37</v>
       </c>
-      <c r="D118" s="19" t="s">
+      <c r="D118" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E118" s="5" t="s">
@@ -5988,17 +5975,17 @@
       </c>
       <c r="J118" s="14"/>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A119" s="20">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A119" s="18">
         <v>18</v>
       </c>
-      <c r="B119" s="23">
+      <c r="B119" s="20">
         <v>6</v>
       </c>
-      <c r="C119" s="19">
+      <c r="C119" s="18">
         <v>38</v>
       </c>
-      <c r="D119" s="19" t="s">
+      <c r="D119" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E119" s="5" t="s">
@@ -6018,17 +6005,17 @@
       </c>
       <c r="J119" s="14"/>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A120" s="20">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A120" s="18">
         <v>21</v>
       </c>
-      <c r="B120" s="23">
+      <c r="B120" s="20">
         <v>5</v>
       </c>
-      <c r="C120" s="19">
+      <c r="C120" s="18">
         <v>39</v>
       </c>
-      <c r="D120" s="19" t="s">
+      <c r="D120" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E120" s="5" t="s">
@@ -6048,197 +6035,197 @@
       </c>
       <c r="J120" s="14"/>
     </row>
-    <row r="121" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="31">
+    <row r="121" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="27">
         <v>32</v>
       </c>
-      <c r="B121" s="35">
+      <c r="B121" s="30">
         <v>1</v>
       </c>
-      <c r="C121" s="32">
+      <c r="C121" s="27">
         <v>40</v>
       </c>
-      <c r="D121" s="32" t="s">
-        <v>402</v>
-      </c>
-      <c r="E121" s="33" t="s">
+      <c r="D121" s="27" t="s">
+        <v>402</v>
+      </c>
+      <c r="E121" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="F121" s="33" t="s">
+      <c r="F121" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="G121" s="33" t="s">
+      <c r="G121" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="H121" s="34">
+      <c r="H121" s="29">
         <v>790000</v>
       </c>
-      <c r="I121" s="33" t="s">
-        <v>407</v>
-      </c>
-      <c r="J121" s="34"/>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A122" s="28">
+      <c r="I121" s="28" t="s">
+        <v>407</v>
+      </c>
+      <c r="J121" s="29"/>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A122" s="24">
         <v>27</v>
       </c>
-      <c r="B122" s="28">
+      <c r="B122" s="24">
         <v>346</v>
       </c>
-      <c r="C122" s="28">
+      <c r="C122" s="24">
         <v>1</v>
       </c>
-      <c r="D122" s="28" t="s">
+      <c r="D122" s="24" t="s">
         <v>401</v>
       </c>
-      <c r="E122" s="29" t="s">
+      <c r="E122" s="25" t="s">
         <v>262</v>
       </c>
-      <c r="F122" s="29" t="s">
+      <c r="F122" s="25" t="s">
         <v>301</v>
       </c>
-      <c r="G122" s="29" t="s">
+      <c r="G122" s="25" t="s">
         <v>302</v>
       </c>
-      <c r="H122" s="44">
+      <c r="H122" s="38">
         <v>5000000</v>
       </c>
-      <c r="I122" s="29" t="s">
+      <c r="I122" s="25" t="s">
         <v>406</v>
       </c>
-      <c r="J122" s="30"/>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A123" s="17">
+      <c r="J122" s="26"/>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A123" s="16">
         <v>20</v>
       </c>
-      <c r="B123" s="17">
+      <c r="B123" s="16">
         <v>307</v>
       </c>
-      <c r="C123" s="17">
+      <c r="C123" s="16">
         <v>2</v>
       </c>
-      <c r="D123" s="17" t="s">
+      <c r="D123" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E123" s="18" t="s">
+      <c r="E123" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="F123" s="18" t="s">
+      <c r="F123" s="17" t="s">
         <v>305</v>
       </c>
-      <c r="G123" s="18" t="s">
+      <c r="G123" s="17" t="s">
         <v>306</v>
       </c>
-      <c r="H123" s="43">
+      <c r="H123" s="37">
         <v>5000000</v>
       </c>
-      <c r="I123" s="18" t="s">
+      <c r="I123" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J123" s="14"/>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A124" s="17">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A124" s="16">
         <v>43</v>
       </c>
-      <c r="B124" s="17">
+      <c r="B124" s="16">
         <v>231</v>
       </c>
-      <c r="C124" s="17">
+      <c r="C124" s="16">
         <v>3</v>
       </c>
-      <c r="D124" s="17" t="s">
+      <c r="D124" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E124" s="18" t="s">
+      <c r="E124" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="F124" s="18" t="s">
+      <c r="F124" s="17" t="s">
         <v>288</v>
       </c>
-      <c r="G124" s="18" t="s">
+      <c r="G124" s="17" t="s">
         <v>289</v>
       </c>
-      <c r="H124" s="43">
+      <c r="H124" s="37">
         <v>5000000</v>
       </c>
-      <c r="I124" s="18" t="s">
+      <c r="I124" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J124" s="14"/>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A125" s="17">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A125" s="16">
         <v>28</v>
       </c>
-      <c r="B125" s="17">
+      <c r="B125" s="16">
         <v>225</v>
       </c>
-      <c r="C125" s="17">
+      <c r="C125" s="16">
         <v>4</v>
       </c>
-      <c r="D125" s="17" t="s">
+      <c r="D125" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E125" s="18" t="s">
+      <c r="E125" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="F125" s="18" t="s">
+      <c r="F125" s="17" t="s">
         <v>325</v>
       </c>
-      <c r="G125" s="18" t="s">
+      <c r="G125" s="17" t="s">
         <v>326</v>
       </c>
-      <c r="H125" s="43">
+      <c r="H125" s="37">
         <v>4000000</v>
       </c>
-      <c r="I125" s="18" t="s">
+      <c r="I125" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J125" s="14"/>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A126" s="17">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A126" s="16">
         <v>12</v>
       </c>
-      <c r="B126" s="17">
+      <c r="B126" s="16">
         <v>214</v>
       </c>
-      <c r="C126" s="17">
+      <c r="C126" s="16">
         <v>5</v>
       </c>
-      <c r="D126" s="17" t="s">
+      <c r="D126" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E126" s="18" t="s">
+      <c r="E126" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="F126" s="18" t="s">
+      <c r="F126" s="17" t="s">
         <v>321</v>
       </c>
-      <c r="G126" s="18" t="s">
+      <c r="G126" s="17" t="s">
         <v>322</v>
       </c>
-      <c r="H126" s="43">
+      <c r="H126" s="37">
         <v>3600000</v>
       </c>
-      <c r="I126" s="18" t="s">
+      <c r="I126" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J126" s="14"/>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A127" s="20">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A127" s="18">
         <v>42</v>
       </c>
-      <c r="B127" s="19">
+      <c r="B127" s="18">
         <v>203</v>
       </c>
-      <c r="C127" s="19">
+      <c r="C127" s="18">
         <v>6</v>
       </c>
-      <c r="D127" s="19" t="s">
+      <c r="D127" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E127" s="5" t="s">
@@ -6258,17 +6245,17 @@
       </c>
       <c r="J127" s="14"/>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A128" s="20">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A128" s="18">
         <v>7</v>
       </c>
-      <c r="B128" s="19">
+      <c r="B128" s="18">
         <v>179</v>
       </c>
-      <c r="C128" s="19">
+      <c r="C128" s="18">
         <v>7</v>
       </c>
-      <c r="D128" s="19" t="s">
+      <c r="D128" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E128" s="5" t="s">
@@ -6286,79 +6273,79 @@
       <c r="I128" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="J128" s="24"/>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A129" s="17">
+      <c r="J128" s="21"/>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A129" s="16">
         <v>22</v>
       </c>
-      <c r="B129" s="17">
+      <c r="B129" s="16">
         <v>171</v>
       </c>
-      <c r="C129" s="17">
+      <c r="C129" s="16">
         <v>8</v>
       </c>
-      <c r="D129" s="17" t="s">
+      <c r="D129" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E129" s="18" t="s">
+      <c r="E129" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="F129" s="18" t="s">
+      <c r="F129" s="17" t="s">
         <v>319</v>
       </c>
-      <c r="G129" s="18" t="s">
+      <c r="G129" s="17" t="s">
         <v>320</v>
       </c>
-      <c r="H129" s="43">
+      <c r="H129" s="37">
         <v>2250000</v>
       </c>
-      <c r="I129" s="18" t="s">
+      <c r="I129" s="17" t="s">
         <v>406</v>
       </c>
-      <c r="J129" s="24"/>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A130" s="19">
+      <c r="J129" s="21"/>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A130" s="18">
         <v>11</v>
       </c>
-      <c r="B130" s="19">
+      <c r="B130" s="18">
         <v>158</v>
       </c>
-      <c r="C130" s="19">
+      <c r="C130" s="18">
         <v>9</v>
       </c>
-      <c r="D130" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="E130" s="21" t="s">
+      <c r="D130" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="E130" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="F130" s="21" t="s">
+      <c r="F130" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="G130" s="21" t="s">
+      <c r="G130" s="5" t="s">
         <v>273</v>
       </c>
-      <c r="H130" s="24">
+      <c r="H130" s="21">
         <v>3100000</v>
       </c>
       <c r="I130" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="J130" s="24"/>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A131" s="20">
+      <c r="J130" s="21"/>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A131" s="18">
         <v>32</v>
       </c>
-      <c r="B131" s="19">
+      <c r="B131" s="18">
         <v>134</v>
       </c>
-      <c r="C131" s="19">
+      <c r="C131" s="18">
         <v>10</v>
       </c>
-      <c r="D131" s="19" t="s">
+      <c r="D131" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E131" s="5" t="s">
@@ -6376,19 +6363,19 @@
       <c r="I131" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="J131" s="24"/>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A132" s="20">
+      <c r="J131" s="21"/>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A132" s="18">
         <v>25</v>
       </c>
-      <c r="B132" s="20">
+      <c r="B132" s="18">
         <v>133</v>
       </c>
-      <c r="C132" s="19">
+      <c r="C132" s="18">
         <v>11</v>
       </c>
-      <c r="D132" s="19" t="s">
+      <c r="D132" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E132" s="5" t="s">
@@ -6408,17 +6395,17 @@
       </c>
       <c r="J132" s="14"/>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A133" s="20">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A133" s="18">
         <v>15</v>
       </c>
-      <c r="B133" s="19">
+      <c r="B133" s="18">
         <v>108</v>
       </c>
-      <c r="C133" s="19">
+      <c r="C133" s="18">
         <v>12</v>
       </c>
-      <c r="D133" s="19" t="s">
+      <c r="D133" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E133" s="5" t="s">
@@ -6438,47 +6425,47 @@
       </c>
       <c r="J133" s="14"/>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A134" s="17">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A134" s="16">
         <v>18</v>
       </c>
-      <c r="B134" s="17">
+      <c r="B134" s="16">
         <v>102</v>
       </c>
-      <c r="C134" s="17">
+      <c r="C134" s="16">
         <v>13</v>
       </c>
-      <c r="D134" s="17" t="s">
+      <c r="D134" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E134" s="18" t="s">
+      <c r="E134" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="F134" s="18" t="s">
+      <c r="F134" s="17" t="s">
         <v>307</v>
       </c>
-      <c r="G134" s="18" t="s">
+      <c r="G134" s="17" t="s">
         <v>308</v>
       </c>
-      <c r="H134" s="43">
+      <c r="H134" s="37">
         <v>668550</v>
       </c>
-      <c r="I134" s="18" t="s">
+      <c r="I134" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J134" s="14"/>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A135" s="20">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A135" s="18">
         <v>10</v>
       </c>
-      <c r="B135" s="19">
+      <c r="B135" s="18">
         <v>97</v>
       </c>
-      <c r="C135" s="19">
+      <c r="C135" s="18">
         <v>14</v>
       </c>
-      <c r="D135" s="19" t="s">
+      <c r="D135" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E135" s="5" t="s">
@@ -6498,17 +6485,17 @@
       </c>
       <c r="J135" s="14"/>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A136" s="20">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A136" s="18">
         <v>16</v>
       </c>
-      <c r="B136" s="19">
+      <c r="B136" s="18">
         <v>91</v>
       </c>
-      <c r="C136" s="19">
+      <c r="C136" s="18">
         <v>15</v>
       </c>
-      <c r="D136" s="19" t="s">
+      <c r="D136" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E136" s="5" t="s">
@@ -6520,7 +6507,7 @@
       <c r="G136" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H136" s="24">
+      <c r="H136" s="21">
         <v>1350000</v>
       </c>
       <c r="I136" s="5" t="s">
@@ -6528,17 +6515,17 @@
       </c>
       <c r="J136" s="14"/>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A137" s="20">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A137" s="18">
         <v>8</v>
       </c>
-      <c r="B137" s="19">
+      <c r="B137" s="18">
         <v>87</v>
       </c>
-      <c r="C137" s="19">
+      <c r="C137" s="18">
         <v>16</v>
       </c>
-      <c r="D137" s="19" t="s">
+      <c r="D137" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E137" s="5" t="s">
@@ -6558,80 +6545,80 @@
       </c>
       <c r="J137" s="14"/>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A138" s="17">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A138" s="16">
         <v>24</v>
       </c>
-      <c r="B138" s="17">
+      <c r="B138" s="16">
         <v>82</v>
       </c>
-      <c r="C138" s="17">
+      <c r="C138" s="16">
         <v>17</v>
       </c>
-      <c r="D138" s="17" t="s">
+      <c r="D138" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E138" s="18" t="s">
+      <c r="E138" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="F138" s="18" t="s">
+      <c r="F138" s="17" t="s">
         <v>315</v>
       </c>
-      <c r="G138" s="18" t="s">
+      <c r="G138" s="17" t="s">
         <v>316</v>
       </c>
-      <c r="H138" s="43">
+      <c r="H138" s="37">
         <v>145000</v>
       </c>
-      <c r="I138" s="18" t="s">
+      <c r="I138" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J138" s="14"/>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A139" s="17">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A139" s="16">
         <v>41</v>
       </c>
-      <c r="B139" s="17">
+      <c r="B139" s="16">
         <v>78</v>
       </c>
-      <c r="C139" s="17">
+      <c r="C139" s="16">
         <v>18</v>
       </c>
-      <c r="D139" s="17" t="s">
+      <c r="D139" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E139" s="18" t="s">
+      <c r="E139" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="F139" s="18" t="s">
+      <c r="F139" s="17" t="s">
         <v>297</v>
       </c>
-      <c r="G139" s="18" t="s">
+      <c r="G139" s="17" t="s">
         <v>298</v>
       </c>
-      <c r="H139" s="43">
+      <c r="H139" s="37">
         <v>435000</v>
       </c>
-      <c r="I139" s="18" t="s">
+      <c r="I139" s="17" t="s">
         <v>406</v>
       </c>
-      <c r="J139" s="22">
+      <c r="J139" s="19">
         <f>SUM(H122:H126,H129,H134,H138:H139)</f>
         <v>26098550</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A140" s="20">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A140" s="18">
         <v>13</v>
       </c>
-      <c r="B140" s="19">
+      <c r="B140" s="18">
         <v>74</v>
       </c>
-      <c r="C140" s="19">
+      <c r="C140" s="18">
         <v>19</v>
       </c>
-      <c r="D140" s="19" t="s">
+      <c r="D140" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E140" s="5" t="s">
@@ -6643,7 +6630,7 @@
       <c r="G140" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="H140" s="24">
+      <c r="H140" s="21">
         <v>897000</v>
       </c>
       <c r="I140" s="5" t="s">
@@ -6651,17 +6638,17 @@
       </c>
       <c r="J140" s="14"/>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A141" s="20">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A141" s="18">
         <v>39</v>
       </c>
-      <c r="B141" s="20">
+      <c r="B141" s="18">
         <v>72</v>
       </c>
-      <c r="C141" s="19">
+      <c r="C141" s="18">
         <v>20</v>
       </c>
-      <c r="D141" s="19" t="s">
+      <c r="D141" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E141" s="5" t="s">
@@ -6681,17 +6668,17 @@
       </c>
       <c r="J141" s="14"/>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A142" s="20">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A142" s="18">
         <v>21</v>
       </c>
-      <c r="B142" s="20">
+      <c r="B142" s="18">
         <v>66</v>
       </c>
-      <c r="C142" s="19">
+      <c r="C142" s="18">
         <v>21</v>
       </c>
-      <c r="D142" s="19" t="s">
+      <c r="D142" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E142" s="5" t="s">
@@ -6711,17 +6698,17 @@
       </c>
       <c r="J142" s="14"/>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A143" s="20">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A143" s="18">
         <v>23</v>
       </c>
-      <c r="B143" s="19">
+      <c r="B143" s="18">
         <v>60</v>
       </c>
-      <c r="C143" s="19">
+      <c r="C143" s="18">
         <v>22</v>
       </c>
-      <c r="D143" s="19" t="s">
+      <c r="D143" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E143" s="5" t="s">
@@ -6741,17 +6728,17 @@
       </c>
       <c r="J143" s="14"/>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A144" s="20">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A144" s="18">
         <v>30</v>
       </c>
-      <c r="B144" s="20">
+      <c r="B144" s="18">
         <v>59</v>
       </c>
-      <c r="C144" s="19">
+      <c r="C144" s="18">
         <v>23</v>
       </c>
-      <c r="D144" s="19" t="s">
+      <c r="D144" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E144" s="5" t="s">
@@ -6771,17 +6758,17 @@
       </c>
       <c r="J144" s="14"/>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A145" s="20">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A145" s="18">
         <v>35</v>
       </c>
-      <c r="B145" s="20">
+      <c r="B145" s="18">
         <v>56</v>
       </c>
-      <c r="C145" s="19">
+      <c r="C145" s="18">
         <v>24</v>
       </c>
-      <c r="D145" s="19" t="s">
+      <c r="D145" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E145" s="5" t="s">
@@ -6793,7 +6780,7 @@
       <c r="G145" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="H145" s="24">
+      <c r="H145" s="21">
         <v>343200</v>
       </c>
       <c r="I145" s="5" t="s">
@@ -6801,17 +6788,17 @@
       </c>
       <c r="J145" s="14"/>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A146" s="20">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A146" s="18">
         <v>19</v>
       </c>
-      <c r="B146" s="20">
+      <c r="B146" s="18">
         <v>50</v>
       </c>
-      <c r="C146" s="19">
+      <c r="C146" s="18">
         <v>25</v>
       </c>
-      <c r="D146" s="19" t="s">
+      <c r="D146" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E146" s="5" t="s">
@@ -6831,17 +6818,17 @@
       </c>
       <c r="J146" s="14"/>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A147" s="20">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A147" s="18">
         <v>37</v>
       </c>
-      <c r="B147" s="27">
+      <c r="B147" s="20">
         <v>49</v>
       </c>
-      <c r="C147" s="19">
+      <c r="C147" s="18">
         <v>26</v>
       </c>
-      <c r="D147" s="19" t="s">
+      <c r="D147" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E147" s="5" t="s">
@@ -6861,17 +6848,17 @@
       </c>
       <c r="J147" s="14"/>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A148" s="20">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A148" s="18">
         <v>17</v>
       </c>
-      <c r="B148" s="27">
+      <c r="B148" s="20">
         <v>48</v>
       </c>
-      <c r="C148" s="19">
+      <c r="C148" s="18">
         <v>27</v>
       </c>
-      <c r="D148" s="19" t="s">
+      <c r="D148" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E148" s="5" t="s">
@@ -6891,17 +6878,17 @@
       </c>
       <c r="J148" s="14"/>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A149" s="20">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A149" s="18">
         <v>34</v>
       </c>
-      <c r="B149" s="27">
+      <c r="B149" s="20">
         <v>46</v>
       </c>
-      <c r="C149" s="19">
+      <c r="C149" s="18">
         <v>28</v>
       </c>
-      <c r="D149" s="19" t="s">
+      <c r="D149" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E149" s="5" t="s">
@@ -6921,17 +6908,17 @@
       </c>
       <c r="J149" s="14"/>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A150" s="20">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A150" s="18">
         <v>1</v>
       </c>
-      <c r="B150" s="27">
+      <c r="B150" s="20">
         <v>44</v>
       </c>
-      <c r="C150" s="19">
+      <c r="C150" s="18">
         <v>29</v>
       </c>
-      <c r="D150" s="19" t="s">
+      <c r="D150" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E150" s="5" t="s">
@@ -6943,7 +6930,7 @@
       <c r="G150" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="H150" s="24">
+      <c r="H150" s="21">
         <v>120000</v>
       </c>
       <c r="I150" s="5" t="s">
@@ -6951,17 +6938,17 @@
       </c>
       <c r="J150" s="14"/>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A151" s="20">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A151" s="18">
         <v>6</v>
       </c>
-      <c r="B151" s="27">
+      <c r="B151" s="20">
         <v>41</v>
       </c>
-      <c r="C151" s="19">
+      <c r="C151" s="18">
         <v>30</v>
       </c>
-      <c r="D151" s="19" t="s">
+      <c r="D151" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E151" s="5" t="s">
@@ -6981,17 +6968,17 @@
       </c>
       <c r="J151" s="14"/>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A152" s="20">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A152" s="18">
         <v>26</v>
       </c>
-      <c r="B152" s="27">
+      <c r="B152" s="20">
         <v>34</v>
       </c>
-      <c r="C152" s="19">
+      <c r="C152" s="18">
         <v>31</v>
       </c>
-      <c r="D152" s="19" t="s">
+      <c r="D152" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E152" s="5" t="s">
@@ -7011,17 +6998,17 @@
       </c>
       <c r="J152" s="14"/>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A153" s="20">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A153" s="18">
         <v>40</v>
       </c>
-      <c r="B153" s="27">
+      <c r="B153" s="20">
         <v>32</v>
       </c>
-      <c r="C153" s="19">
+      <c r="C153" s="18">
         <v>32</v>
       </c>
-      <c r="D153" s="19" t="s">
+      <c r="D153" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E153" s="5" t="s">
@@ -7041,17 +7028,17 @@
       </c>
       <c r="J153" s="14"/>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A154" s="20">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A154" s="18">
         <v>33</v>
       </c>
-      <c r="B154" s="27">
+      <c r="B154" s="20">
         <v>29</v>
       </c>
-      <c r="C154" s="19">
+      <c r="C154" s="18">
         <v>33</v>
       </c>
-      <c r="D154" s="19" t="s">
+      <c r="D154" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E154" s="5" t="s">
@@ -7071,17 +7058,17 @@
       </c>
       <c r="J154" s="14"/>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A155" s="20">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A155" s="18">
         <v>31</v>
       </c>
-      <c r="B155" s="27">
+      <c r="B155" s="20">
         <v>27</v>
       </c>
-      <c r="C155" s="19">
+      <c r="C155" s="18">
         <v>34</v>
       </c>
-      <c r="D155" s="19" t="s">
+      <c r="D155" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E155" s="5" t="s">
@@ -7101,17 +7088,17 @@
       </c>
       <c r="J155" s="14"/>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A156" s="20">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A156" s="18">
         <v>2</v>
       </c>
-      <c r="B156" s="27">
+      <c r="B156" s="20">
         <v>21</v>
       </c>
-      <c r="C156" s="19">
+      <c r="C156" s="18">
         <v>35</v>
       </c>
-      <c r="D156" s="19" t="s">
+      <c r="D156" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E156" s="5" t="s">
@@ -7131,17 +7118,17 @@
       </c>
       <c r="J156" s="14"/>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A157" s="20">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A157" s="18">
         <v>36</v>
       </c>
-      <c r="B157" s="27">
+      <c r="B157" s="20">
         <v>20</v>
       </c>
-      <c r="C157" s="19">
+      <c r="C157" s="18">
         <v>36</v>
       </c>
-      <c r="D157" s="19" t="s">
+      <c r="D157" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E157" s="5" t="s">
@@ -7161,17 +7148,17 @@
       </c>
       <c r="J157" s="14"/>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A158" s="20">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A158" s="18">
         <v>38</v>
       </c>
-      <c r="B158" s="27">
+      <c r="B158" s="20">
         <v>19</v>
       </c>
-      <c r="C158" s="19">
+      <c r="C158" s="18">
         <v>37</v>
       </c>
-      <c r="D158" s="19" t="s">
+      <c r="D158" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E158" s="5" t="s">
@@ -7191,17 +7178,17 @@
       </c>
       <c r="J158" s="14"/>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A159" s="20">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A159" s="18">
         <v>5</v>
       </c>
-      <c r="B159" s="27">
+      <c r="B159" s="20">
         <v>15</v>
       </c>
-      <c r="C159" s="19">
+      <c r="C159" s="18">
         <v>38</v>
       </c>
-      <c r="D159" s="19" t="s">
+      <c r="D159" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E159" s="5" t="s">
@@ -7221,17 +7208,17 @@
       </c>
       <c r="J159" s="14"/>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A160" s="20">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A160" s="18">
         <v>14</v>
       </c>
-      <c r="B160" s="27">
+      <c r="B160" s="20">
         <v>14</v>
       </c>
-      <c r="C160" s="19">
+      <c r="C160" s="18">
         <v>39</v>
       </c>
-      <c r="D160" s="19" t="s">
+      <c r="D160" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E160" s="5" t="s">
@@ -7251,17 +7238,17 @@
       </c>
       <c r="J160" s="14"/>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A161" s="20">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A161" s="18">
         <v>4</v>
       </c>
-      <c r="B161" s="27">
+      <c r="B161" s="20">
         <v>13</v>
       </c>
-      <c r="C161" s="19">
+      <c r="C161" s="18">
         <v>40</v>
       </c>
-      <c r="D161" s="19" t="s">
+      <c r="D161" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E161" s="5" t="s">
@@ -7281,17 +7268,17 @@
       </c>
       <c r="J161" s="14"/>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A162" s="20">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A162" s="18">
         <v>9</v>
       </c>
-      <c r="B162" s="27">
+      <c r="B162" s="20">
         <v>9</v>
       </c>
-      <c r="C162" s="19">
+      <c r="C162" s="18">
         <v>41</v>
       </c>
-      <c r="D162" s="19" t="s">
+      <c r="D162" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E162" s="5" t="s">
@@ -7311,17 +7298,17 @@
       </c>
       <c r="J162" s="14"/>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A163" s="20">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A163" s="18">
         <v>29</v>
       </c>
-      <c r="B163" s="27">
+      <c r="B163" s="20">
         <v>8</v>
       </c>
-      <c r="C163" s="19">
+      <c r="C163" s="18">
         <v>42</v>
       </c>
-      <c r="D163" s="19" t="s">
+      <c r="D163" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E163" s="5" t="s">
@@ -7341,209 +7328,209 @@
       </c>
       <c r="J163" s="14"/>
     </row>
-    <row r="164" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="31">
+    <row r="164" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A164" s="27">
         <v>3</v>
       </c>
-      <c r="B164" s="36">
+      <c r="B164" s="30">
         <v>7</v>
       </c>
-      <c r="C164" s="32">
+      <c r="C164" s="27">
         <v>43</v>
       </c>
-      <c r="D164" s="32" t="s">
-        <v>402</v>
-      </c>
-      <c r="E164" s="33" t="s">
+      <c r="D164" s="27" t="s">
+        <v>402</v>
+      </c>
+      <c r="E164" s="28" t="s">
         <v>262</v>
       </c>
-      <c r="F164" s="33" t="s">
+      <c r="F164" s="28" t="s">
         <v>327</v>
       </c>
-      <c r="G164" s="33" t="s">
+      <c r="G164" s="28" t="s">
         <v>328</v>
       </c>
-      <c r="H164" s="34">
+      <c r="H164" s="29">
         <v>1680000</v>
       </c>
-      <c r="I164" s="33" t="s">
-        <v>407</v>
-      </c>
-      <c r="J164" s="34"/>
-    </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A165" s="28">
+      <c r="I164" s="28" t="s">
+        <v>407</v>
+      </c>
+      <c r="J164" s="29"/>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A165" s="24">
         <v>11</v>
       </c>
-      <c r="B165" s="28">
+      <c r="B165" s="24">
         <v>345</v>
       </c>
-      <c r="C165" s="28">
+      <c r="C165" s="24">
         <v>1</v>
       </c>
-      <c r="D165" s="28" t="s">
+      <c r="D165" s="24" t="s">
         <v>401</v>
       </c>
-      <c r="E165" s="29" t="s">
+      <c r="E165" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="F165" s="29" t="s">
+      <c r="F165" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="G165" s="29" t="s">
+      <c r="G165" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="H165" s="44">
+      <c r="H165" s="38">
         <v>2130000</v>
       </c>
-      <c r="I165" s="29" t="s">
+      <c r="I165" s="25" t="s">
         <v>406</v>
       </c>
-      <c r="J165" s="30"/>
-    </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A166" s="17">
+      <c r="J165" s="26"/>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A166" s="16">
         <v>9</v>
       </c>
-      <c r="B166" s="17">
+      <c r="B166" s="16">
         <v>152</v>
       </c>
-      <c r="C166" s="17">
+      <c r="C166" s="16">
         <v>2</v>
       </c>
-      <c r="D166" s="17" t="s">
+      <c r="D166" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E166" s="18" t="s">
+      <c r="E166" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F166" s="18" t="s">
+      <c r="F166" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="G166" s="18" t="s">
+      <c r="G166" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="H166" s="43">
+      <c r="H166" s="37">
         <v>4760000</v>
       </c>
-      <c r="I166" s="18" t="s">
+      <c r="I166" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J166" s="14"/>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A167" s="17">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A167" s="16">
         <v>13</v>
       </c>
-      <c r="B167" s="17">
+      <c r="B167" s="16">
         <v>82</v>
       </c>
-      <c r="C167" s="17">
+      <c r="C167" s="16">
         <v>3</v>
       </c>
-      <c r="D167" s="17" t="s">
+      <c r="D167" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E167" s="18" t="s">
+      <c r="E167" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F167" s="18" t="s">
+      <c r="F167" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="G167" s="18" t="s">
+      <c r="G167" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="H167" s="43">
+      <c r="H167" s="37">
         <v>5000000</v>
       </c>
-      <c r="I167" s="18" t="s">
+      <c r="I167" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J167" s="14"/>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A168" s="17">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A168" s="16">
         <v>12</v>
       </c>
-      <c r="B168" s="17">
+      <c r="B168" s="16">
         <v>74</v>
       </c>
-      <c r="C168" s="17">
+      <c r="C168" s="16">
         <v>4</v>
       </c>
-      <c r="D168" s="17" t="s">
+      <c r="D168" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E168" s="18" t="s">
+      <c r="E168" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F168" s="18" t="s">
+      <c r="F168" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="G168" s="18" t="s">
+      <c r="G168" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="H168" s="43">
+      <c r="H168" s="37">
         <v>5000000</v>
       </c>
-      <c r="I168" s="18" t="s">
+      <c r="I168" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J168" s="14"/>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A169" s="17">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A169" s="16">
         <v>19</v>
       </c>
-      <c r="B169" s="17">
+      <c r="B169" s="16">
         <v>66</v>
       </c>
-      <c r="C169" s="17">
+      <c r="C169" s="16">
         <v>5</v>
       </c>
-      <c r="D169" s="17" t="s">
+      <c r="D169" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E169" s="18" t="s">
+      <c r="E169" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F169" s="18" t="s">
+      <c r="F169" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="G169" s="18" t="s">
+      <c r="G169" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="H169" s="43">
+      <c r="H169" s="37">
         <v>5000000</v>
       </c>
-      <c r="I169" s="18" t="s">
+      <c r="I169" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J169" s="14"/>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A170" s="19">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A170" s="18">
         <v>7</v>
       </c>
-      <c r="B170" s="20">
+      <c r="B170" s="18">
         <v>60</v>
       </c>
-      <c r="C170" s="19">
+      <c r="C170" s="18">
         <v>6</v>
       </c>
-      <c r="D170" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="E170" s="21" t="s">
+      <c r="D170" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="E170" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F170" s="21" t="s">
+      <c r="F170" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G170" s="21" t="s">
+      <c r="G170" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H170" s="24">
+      <c r="H170" s="21">
         <v>495000</v>
       </c>
       <c r="I170" s="5" t="s">
@@ -7551,29 +7538,29 @@
       </c>
       <c r="J170" s="14"/>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A171" s="19">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A171" s="18">
         <v>17</v>
       </c>
-      <c r="B171" s="19">
+      <c r="B171" s="18">
         <v>50</v>
       </c>
-      <c r="C171" s="19">
+      <c r="C171" s="18">
         <v>7</v>
       </c>
-      <c r="D171" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="E171" s="21" t="s">
+      <c r="D171" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="E171" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F171" s="21" t="s">
+      <c r="F171" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G171" s="21" t="s">
+      <c r="G171" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H171" s="24">
+      <c r="H171" s="21">
         <v>1350000</v>
       </c>
       <c r="I171" s="5" t="s">
@@ -7581,29 +7568,29 @@
       </c>
       <c r="J171" s="14"/>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A172" s="19">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A172" s="18">
         <v>20</v>
       </c>
-      <c r="B172" s="19">
+      <c r="B172" s="18">
         <v>32</v>
       </c>
-      <c r="C172" s="19">
+      <c r="C172" s="18">
         <v>8</v>
       </c>
-      <c r="D172" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="E172" s="21" t="s">
+      <c r="D172" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="E172" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F172" s="21" t="s">
+      <c r="F172" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G172" s="21" t="s">
+      <c r="G172" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="H172" s="24">
+      <c r="H172" s="21">
         <v>533000</v>
       </c>
       <c r="I172" s="5" t="s">
@@ -7611,29 +7598,29 @@
       </c>
       <c r="J172" s="14"/>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A173" s="19">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A173" s="18">
         <v>8</v>
       </c>
-      <c r="B173" s="19">
+      <c r="B173" s="18">
         <v>27</v>
       </c>
-      <c r="C173" s="19">
+      <c r="C173" s="18">
         <v>9</v>
       </c>
-      <c r="D173" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="E173" s="21" t="s">
+      <c r="D173" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="E173" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F173" s="21" t="s">
+      <c r="F173" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G173" s="21" t="s">
+      <c r="G173" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="H173" s="24">
+      <c r="H173" s="21">
         <v>881000</v>
       </c>
       <c r="I173" s="5" t="s">
@@ -7641,29 +7628,29 @@
       </c>
       <c r="J173" s="14"/>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A174" s="19">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A174" s="18">
         <v>18</v>
       </c>
-      <c r="B174" s="19">
+      <c r="B174" s="18">
         <v>27</v>
       </c>
-      <c r="C174" s="19">
+      <c r="C174" s="18">
         <v>10</v>
       </c>
-      <c r="D174" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="E174" s="21" t="s">
+      <c r="D174" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="E174" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F174" s="21" t="s">
+      <c r="F174" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G174" s="21" t="s">
+      <c r="G174" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="H174" s="24">
+      <c r="H174" s="21">
         <v>630000</v>
       </c>
       <c r="I174" s="5" t="s">
@@ -7671,29 +7658,29 @@
       </c>
       <c r="J174" s="14"/>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A175" s="19">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A175" s="18">
         <v>6</v>
       </c>
-      <c r="B175" s="19">
+      <c r="B175" s="18">
         <v>24</v>
       </c>
-      <c r="C175" s="19">
+      <c r="C175" s="18">
         <v>11</v>
       </c>
-      <c r="D175" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="E175" s="21" t="s">
+      <c r="D175" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="E175" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F175" s="21" t="s">
+      <c r="F175" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G175" s="21" t="s">
+      <c r="G175" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H175" s="24">
+      <c r="H175" s="21">
         <v>1608000</v>
       </c>
       <c r="I175" s="5" t="s">
@@ -7701,47 +7688,47 @@
       </c>
       <c r="J175" s="14"/>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A176" s="19">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A176" s="18">
         <v>2</v>
       </c>
-      <c r="B176" s="20">
+      <c r="B176" s="18">
         <v>20</v>
       </c>
-      <c r="C176" s="19">
+      <c r="C176" s="18">
         <v>12</v>
       </c>
-      <c r="D176" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="E176" s="21" t="s">
+      <c r="D176" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="E176" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F176" s="21" t="s">
+      <c r="F176" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="G176" s="21" t="s">
+      <c r="G176" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="H176" s="24">
+      <c r="H176" s="21">
         <v>1074000</v>
       </c>
       <c r="I176" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="J176" s="26"/>
-    </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A177" s="20">
+      <c r="J176" s="23"/>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A177" s="18">
         <v>15</v>
       </c>
-      <c r="B177" s="20">
+      <c r="B177" s="18">
         <v>19</v>
       </c>
-      <c r="C177" s="19">
+      <c r="C177" s="18">
         <v>13</v>
       </c>
-      <c r="D177" s="19" t="s">
+      <c r="D177" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E177" s="5" t="s">
@@ -7761,50 +7748,50 @@
       </c>
       <c r="J177" s="14"/>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A178" s="17">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A178" s="16">
         <v>1</v>
       </c>
-      <c r="B178" s="17">
+      <c r="B178" s="16">
         <v>16</v>
       </c>
-      <c r="C178" s="17">
+      <c r="C178" s="16">
         <v>14</v>
       </c>
-      <c r="D178" s="17" t="s">
+      <c r="D178" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E178" s="18" t="s">
+      <c r="E178" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F178" s="18" t="s">
+      <c r="F178" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="G178" s="18" t="s">
+      <c r="G178" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="H178" s="43">
+      <c r="H178" s="37">
         <v>120000</v>
       </c>
-      <c r="I178" s="18" t="s">
+      <c r="I178" s="17" t="s">
         <v>406</v>
       </c>
-      <c r="J178" s="22">
+      <c r="J178" s="19">
         <f>SUM(H165:H169,H178)</f>
         <v>22010000</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A179" s="20">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A179" s="18">
         <v>3</v>
       </c>
-      <c r="B179" s="23">
+      <c r="B179" s="20">
         <v>15</v>
       </c>
-      <c r="C179" s="19">
+      <c r="C179" s="18">
         <v>15</v>
       </c>
-      <c r="D179" s="19" t="s">
+      <c r="D179" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E179" s="5" t="s">
@@ -7824,17 +7811,17 @@
       </c>
       <c r="J179" s="14"/>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A180" s="20">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A180" s="18">
         <v>16</v>
       </c>
-      <c r="B180" s="23">
+      <c r="B180" s="20">
         <v>14</v>
       </c>
-      <c r="C180" s="19">
+      <c r="C180" s="18">
         <v>16</v>
       </c>
-      <c r="D180" s="19" t="s">
+      <c r="D180" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E180" s="5" t="s">
@@ -7854,17 +7841,17 @@
       </c>
       <c r="J180" s="14"/>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A181" s="20">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A181" s="18">
         <v>14</v>
       </c>
-      <c r="B181" s="23">
+      <c r="B181" s="20">
         <v>11</v>
       </c>
-      <c r="C181" s="19">
+      <c r="C181" s="18">
         <v>17</v>
       </c>
-      <c r="D181" s="19" t="s">
+      <c r="D181" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E181" s="5" t="s">
@@ -7884,17 +7871,17 @@
       </c>
       <c r="J181" s="14"/>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A182" s="20">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A182" s="18">
         <v>5</v>
       </c>
-      <c r="B182" s="23">
+      <c r="B182" s="20">
         <v>9</v>
       </c>
-      <c r="C182" s="19">
+      <c r="C182" s="18">
         <v>18</v>
       </c>
-      <c r="D182" s="19" t="s">
+      <c r="D182" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E182" s="5" t="s">
@@ -7914,17 +7901,17 @@
       </c>
       <c r="J182" s="14"/>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A183" s="20">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A183" s="18">
         <v>4</v>
       </c>
-      <c r="B183" s="23">
+      <c r="B183" s="20">
         <v>7</v>
       </c>
-      <c r="C183" s="19">
+      <c r="C183" s="18">
         <v>19</v>
       </c>
-      <c r="D183" s="19" t="s">
+      <c r="D183" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E183" s="5" t="s">
@@ -7944,257 +7931,257 @@
       </c>
       <c r="J183" s="14"/>
     </row>
-    <row r="184" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="31">
+    <row r="184" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A184" s="27">
         <v>10</v>
       </c>
-      <c r="B184" s="35">
+      <c r="B184" s="30">
         <v>5</v>
       </c>
-      <c r="C184" s="32">
+      <c r="C184" s="27">
         <v>20</v>
       </c>
-      <c r="D184" s="32" t="s">
-        <v>402</v>
-      </c>
-      <c r="E184" s="33" t="s">
+      <c r="D184" s="27" t="s">
+        <v>402</v>
+      </c>
+      <c r="E184" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="F184" s="33" t="s">
+      <c r="F184" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="G184" s="33" t="s">
+      <c r="G184" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="H184" s="34">
+      <c r="H184" s="29">
         <v>5000000</v>
       </c>
-      <c r="I184" s="33" t="s">
-        <v>407</v>
-      </c>
-      <c r="J184" s="34"/>
-    </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A185" s="28">
+      <c r="I184" s="28" t="s">
+        <v>407</v>
+      </c>
+      <c r="J184" s="29"/>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A185" s="24">
         <v>2</v>
       </c>
-      <c r="B185" s="28">
+      <c r="B185" s="24">
         <v>429</v>
       </c>
-      <c r="C185" s="28">
+      <c r="C185" s="24">
         <v>1</v>
       </c>
-      <c r="D185" s="28" t="s">
+      <c r="D185" s="24" t="s">
         <v>401</v>
       </c>
-      <c r="E185" s="29" t="s">
+      <c r="E185" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="F185" s="29" t="s">
+      <c r="F185" s="25" t="s">
         <v>156</v>
       </c>
-      <c r="G185" s="29" t="s">
+      <c r="G185" s="25" t="s">
         <v>157</v>
       </c>
-      <c r="H185" s="44">
+      <c r="H185" s="38">
         <v>4250000</v>
       </c>
-      <c r="I185" s="29" t="s">
+      <c r="I185" s="25" t="s">
         <v>406</v>
       </c>
-      <c r="J185" s="30"/>
-    </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A186" s="17">
+      <c r="J185" s="26"/>
+    </row>
+    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A186" s="16">
         <v>3</v>
       </c>
-      <c r="B186" s="17">
+      <c r="B186" s="16">
         <v>126</v>
       </c>
-      <c r="C186" s="17">
+      <c r="C186" s="16">
         <v>2</v>
       </c>
-      <c r="D186" s="17" t="s">
+      <c r="D186" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E186" s="18" t="s">
+      <c r="E186" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="F186" s="18" t="s">
+      <c r="F186" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="G186" s="18" t="s">
+      <c r="G186" s="17" t="s">
         <v>159</v>
       </c>
-      <c r="H186" s="43">
+      <c r="H186" s="37">
         <v>5000000</v>
       </c>
-      <c r="I186" s="18" t="s">
+      <c r="I186" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J186" s="14"/>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A187" s="17">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A187" s="16">
         <v>6</v>
       </c>
-      <c r="B187" s="17">
+      <c r="B187" s="16">
         <v>37</v>
       </c>
-      <c r="C187" s="17">
+      <c r="C187" s="16">
         <v>3</v>
       </c>
-      <c r="D187" s="17" t="s">
+      <c r="D187" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E187" s="18" t="s">
+      <c r="E187" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="F187" s="18" t="s">
+      <c r="F187" s="17" t="s">
         <v>162</v>
       </c>
-      <c r="G187" s="18" t="s">
+      <c r="G187" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="H187" s="43">
+      <c r="H187" s="37">
         <v>2100000</v>
       </c>
-      <c r="I187" s="18" t="s">
+      <c r="I187" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J187" s="14"/>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A188" s="17">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A188" s="16">
         <v>1</v>
       </c>
-      <c r="B188" s="17">
+      <c r="B188" s="16">
         <v>35</v>
       </c>
-      <c r="C188" s="17">
+      <c r="C188" s="16">
         <v>4</v>
       </c>
-      <c r="D188" s="17" t="s">
+      <c r="D188" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E188" s="18" t="s">
+      <c r="E188" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="F188" s="18" t="s">
+      <c r="F188" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="G188" s="18" t="s">
+      <c r="G188" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="H188" s="43">
+      <c r="H188" s="37">
         <v>723000</v>
       </c>
-      <c r="I188" s="18" t="s">
+      <c r="I188" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J188" s="14"/>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A189" s="17">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A189" s="16">
         <v>4</v>
       </c>
-      <c r="B189" s="17">
+      <c r="B189" s="16">
         <v>19</v>
       </c>
-      <c r="C189" s="17">
+      <c r="C189" s="16">
         <v>5</v>
       </c>
-      <c r="D189" s="17" t="s">
+      <c r="D189" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E189" s="18" t="s">
+      <c r="E189" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="F189" s="18" t="s">
+      <c r="F189" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="G189" s="18" t="s">
+      <c r="G189" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="H189" s="43">
+      <c r="H189" s="37">
         <v>372000</v>
       </c>
-      <c r="I189" s="18" t="s">
+      <c r="I189" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J189" s="14"/>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A190" s="17">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A190" s="16">
         <v>5</v>
       </c>
-      <c r="B190" s="17">
+      <c r="B190" s="16">
         <v>13</v>
       </c>
-      <c r="C190" s="17">
+      <c r="C190" s="16">
         <v>6</v>
       </c>
-      <c r="D190" s="17" t="s">
+      <c r="D190" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E190" s="18" t="s">
+      <c r="E190" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="F190" s="18" t="s">
+      <c r="F190" s="17" t="s">
         <v>160</v>
       </c>
-      <c r="G190" s="18" t="s">
+      <c r="G190" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="H190" s="43">
+      <c r="H190" s="37">
         <v>623000</v>
       </c>
-      <c r="I190" s="18" t="s">
+      <c r="I190" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J190" s="14"/>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A191" s="17">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A191" s="16">
         <v>8</v>
       </c>
-      <c r="B191" s="17">
+      <c r="B191" s="16">
         <v>13</v>
       </c>
-      <c r="C191" s="17">
+      <c r="C191" s="16">
         <v>7</v>
       </c>
-      <c r="D191" s="17" t="s">
+      <c r="D191" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E191" s="18" t="s">
+      <c r="E191" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="F191" s="18" t="s">
+      <c r="F191" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="G191" s="18" t="s">
+      <c r="G191" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="H191" s="43">
+      <c r="H191" s="37">
         <v>5000000</v>
       </c>
-      <c r="I191" s="18" t="s">
+      <c r="I191" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J191" s="14"/>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A192" s="20">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A192" s="18">
         <v>7</v>
       </c>
-      <c r="B192" s="20">
+      <c r="B192" s="18">
         <v>9</v>
       </c>
-      <c r="C192" s="19">
+      <c r="C192" s="18">
         <v>8</v>
       </c>
-      <c r="D192" s="19" t="s">
+      <c r="D192" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E192" s="5" t="s">
@@ -8214,212 +8201,212 @@
       </c>
       <c r="J192" s="14"/>
     </row>
-    <row r="193" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="37">
+    <row r="193" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A193" s="31">
         <v>9</v>
       </c>
-      <c r="B193" s="38">
+      <c r="B193" s="32">
         <v>9</v>
       </c>
-      <c r="C193" s="37">
+      <c r="C193" s="31">
         <v>9</v>
       </c>
-      <c r="D193" s="37" t="s">
+      <c r="D193" s="31" t="s">
         <v>401</v>
       </c>
-      <c r="E193" s="39" t="s">
+      <c r="E193" s="33" t="s">
         <v>149</v>
       </c>
-      <c r="F193" s="39" t="s">
+      <c r="F193" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="G193" s="39" t="s">
+      <c r="G193" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="H193" s="45">
+      <c r="H193" s="39">
         <v>162000</v>
       </c>
-      <c r="I193" s="39" t="s">
+      <c r="I193" s="33" t="s">
         <v>406</v>
       </c>
-      <c r="J193" s="40">
+      <c r="J193" s="34">
         <f>SUM(H185:H191,H193)</f>
         <v>18230000</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A194" s="28">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A194" s="24">
         <v>2</v>
       </c>
-      <c r="B194" s="28">
+      <c r="B194" s="24">
         <v>1439</v>
       </c>
-      <c r="C194" s="28">
+      <c r="C194" s="24">
         <v>1</v>
       </c>
-      <c r="D194" s="28" t="s">
+      <c r="D194" s="24" t="s">
         <v>401</v>
       </c>
-      <c r="E194" s="29" t="s">
+      <c r="E194" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="F194" s="29" t="s">
+      <c r="F194" s="25" t="s">
         <v>246</v>
       </c>
-      <c r="G194" s="29" t="s">
+      <c r="G194" s="25" t="s">
         <v>247</v>
       </c>
-      <c r="H194" s="44">
+      <c r="H194" s="38">
         <v>5000000</v>
       </c>
-      <c r="I194" s="29" t="s">
+      <c r="I194" s="25" t="s">
         <v>406</v>
       </c>
-      <c r="J194" s="30"/>
-    </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A195" s="17">
+      <c r="J194" s="26"/>
+    </row>
+    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A195" s="16">
         <v>22</v>
       </c>
-      <c r="B195" s="17">
+      <c r="B195" s="16">
         <v>758</v>
       </c>
-      <c r="C195" s="17">
+      <c r="C195" s="16">
         <v>2</v>
       </c>
-      <c r="D195" s="17" t="s">
+      <c r="D195" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E195" s="18" t="s">
+      <c r="E195" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="F195" s="18" t="s">
+      <c r="F195" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="G195" s="18" t="s">
+      <c r="G195" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="H195" s="43">
+      <c r="H195" s="37">
         <v>3800000</v>
       </c>
-      <c r="I195" s="18" t="s">
+      <c r="I195" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J195" s="14"/>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A196" s="17">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A196" s="16">
         <v>1</v>
       </c>
-      <c r="B196" s="17">
+      <c r="B196" s="16">
         <v>752</v>
       </c>
-      <c r="C196" s="17">
+      <c r="C196" s="16">
         <v>3</v>
       </c>
-      <c r="D196" s="17" t="s">
+      <c r="D196" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E196" s="18" t="s">
+      <c r="E196" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="F196" s="18" t="s">
+      <c r="F196" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="G196" s="18" t="s">
+      <c r="G196" s="17" t="s">
         <v>224</v>
       </c>
-      <c r="H196" s="43">
+      <c r="H196" s="37">
         <v>3900000</v>
       </c>
-      <c r="I196" s="18" t="s">
+      <c r="I196" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J196" s="14"/>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A197" s="17">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A197" s="16">
         <v>10</v>
       </c>
-      <c r="B197" s="17">
+      <c r="B197" s="16">
         <v>209</v>
       </c>
-      <c r="C197" s="17">
+      <c r="C197" s="16">
         <v>4</v>
       </c>
-      <c r="D197" s="17" t="s">
+      <c r="D197" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E197" s="18" t="s">
+      <c r="E197" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="F197" s="18" t="s">
+      <c r="F197" s="17" t="s">
         <v>256</v>
       </c>
-      <c r="G197" s="18" t="s">
+      <c r="G197" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="H197" s="43">
+      <c r="H197" s="37">
         <v>2191200</v>
       </c>
-      <c r="I197" s="18" t="s">
+      <c r="I197" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J197" s="14"/>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A198" s="17">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A198" s="16">
         <v>24</v>
       </c>
-      <c r="B198" s="17">
+      <c r="B198" s="16">
         <v>91</v>
       </c>
-      <c r="C198" s="17">
+      <c r="C198" s="16">
         <v>5</v>
       </c>
-      <c r="D198" s="17" t="s">
+      <c r="D198" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E198" s="18" t="s">
+      <c r="E198" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="F198" s="18" t="s">
+      <c r="F198" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="G198" s="18" t="s">
+      <c r="G198" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="H198" s="43">
+      <c r="H198" s="37">
         <v>5000000</v>
       </c>
-      <c r="I198" s="18" t="s">
+      <c r="I198" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J198" s="14"/>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A199" s="19">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A199" s="18">
         <v>4</v>
       </c>
-      <c r="B199" s="20">
+      <c r="B199" s="18">
         <v>79</v>
       </c>
-      <c r="C199" s="19">
+      <c r="C199" s="18">
         <v>6</v>
       </c>
-      <c r="D199" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="E199" s="21" t="s">
+      <c r="D199" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="E199" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="F199" s="21" t="s">
+      <c r="F199" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="G199" s="21" t="s">
+      <c r="G199" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="H199" s="24">
+      <c r="H199" s="21">
         <v>3660000</v>
       </c>
       <c r="I199" s="5" t="s">
@@ -8427,17 +8414,17 @@
       </c>
       <c r="J199" s="14"/>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A200" s="20">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A200" s="18">
         <v>11</v>
       </c>
-      <c r="B200" s="20">
+      <c r="B200" s="18">
         <v>76</v>
       </c>
-      <c r="C200" s="19">
+      <c r="C200" s="18">
         <v>7</v>
       </c>
-      <c r="D200" s="19" t="s">
+      <c r="D200" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E200" s="5" t="s">
@@ -8449,7 +8436,7 @@
       <c r="G200" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="H200" s="24">
+      <c r="H200" s="21">
         <v>3000000</v>
       </c>
       <c r="I200" s="5" t="s">
@@ -8457,17 +8444,17 @@
       </c>
       <c r="J200" s="14"/>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A201" s="20">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A201" s="18">
         <v>19</v>
       </c>
-      <c r="B201" s="20">
+      <c r="B201" s="18">
         <v>53</v>
       </c>
-      <c r="C201" s="19">
+      <c r="C201" s="18">
         <v>8</v>
       </c>
-      <c r="D201" s="19" t="s">
+      <c r="D201" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E201" s="5" t="s">
@@ -8479,7 +8466,7 @@
       <c r="G201" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="H201" s="24">
+      <c r="H201" s="21">
         <v>5000000</v>
       </c>
       <c r="I201" s="5" t="s">
@@ -8487,77 +8474,77 @@
       </c>
       <c r="J201" s="14"/>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A202" s="17">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A202" s="16">
         <v>3</v>
       </c>
-      <c r="B202" s="17">
+      <c r="B202" s="16">
         <v>48</v>
       </c>
-      <c r="C202" s="17">
+      <c r="C202" s="16">
         <v>9</v>
       </c>
-      <c r="D202" s="17" t="s">
+      <c r="D202" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E202" s="18" t="s">
+      <c r="E202" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="F202" s="18" t="s">
+      <c r="F202" s="17" t="s">
         <v>238</v>
       </c>
-      <c r="G202" s="18" t="s">
+      <c r="G202" s="17" t="s">
         <v>239</v>
       </c>
-      <c r="H202" s="43">
+      <c r="H202" s="37">
         <v>1500000</v>
       </c>
-      <c r="I202" s="18" t="s">
+      <c r="I202" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J202" s="14"/>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A203" s="17">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A203" s="16">
         <v>25</v>
       </c>
-      <c r="B203" s="17">
+      <c r="B203" s="16">
         <v>34</v>
       </c>
-      <c r="C203" s="17">
+      <c r="C203" s="16">
         <v>10</v>
       </c>
-      <c r="D203" s="17" t="s">
+      <c r="D203" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E203" s="18" t="s">
+      <c r="E203" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="F203" s="18" t="s">
+      <c r="F203" s="17" t="s">
         <v>250</v>
       </c>
-      <c r="G203" s="18" t="s">
+      <c r="G203" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="H203" s="43">
+      <c r="H203" s="37">
         <v>400000</v>
       </c>
-      <c r="I203" s="18" t="s">
+      <c r="I203" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J203" s="14"/>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A204" s="20">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A204" s="18">
         <v>14</v>
       </c>
-      <c r="B204" s="20">
+      <c r="B204" s="18">
         <v>30</v>
       </c>
-      <c r="C204" s="19">
+      <c r="C204" s="18">
         <v>11</v>
       </c>
-      <c r="D204" s="19" t="s">
+      <c r="D204" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E204" s="5" t="s">
@@ -8577,29 +8564,29 @@
       </c>
       <c r="J204" s="14"/>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A205" s="19">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A205" s="18">
         <v>5</v>
       </c>
-      <c r="B205" s="20">
+      <c r="B205" s="18">
         <v>29</v>
       </c>
-      <c r="C205" s="19">
+      <c r="C205" s="18">
         <v>12</v>
       </c>
-      <c r="D205" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="E205" s="21" t="s">
+      <c r="D205" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="E205" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="F205" s="21" t="s">
+      <c r="F205" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G205" s="21" t="s">
+      <c r="G205" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H205" s="24">
+      <c r="H205" s="21">
         <v>675000</v>
       </c>
       <c r="I205" s="5" t="s">
@@ -8607,29 +8594,29 @@
       </c>
       <c r="J205" s="14"/>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A206" s="19">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A206" s="18">
         <v>17</v>
       </c>
-      <c r="B206" s="20">
+      <c r="B206" s="18">
         <v>25</v>
       </c>
-      <c r="C206" s="19">
+      <c r="C206" s="18">
         <v>13</v>
       </c>
-      <c r="D206" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="E206" s="21" t="s">
+      <c r="D206" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="E206" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="F206" s="21" t="s">
+      <c r="F206" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="G206" s="21" t="s">
+      <c r="G206" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="H206" s="24">
+      <c r="H206" s="21">
         <v>558000</v>
       </c>
       <c r="I206" s="5" t="s">
@@ -8637,29 +8624,29 @@
       </c>
       <c r="J206" s="14"/>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A207" s="19">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A207" s="18">
         <v>18</v>
       </c>
-      <c r="B207" s="20">
+      <c r="B207" s="18">
         <v>21</v>
       </c>
-      <c r="C207" s="19">
+      <c r="C207" s="18">
         <v>14</v>
       </c>
-      <c r="D207" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="E207" s="21" t="s">
+      <c r="D207" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="E207" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="F207" s="21" t="s">
+      <c r="F207" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="G207" s="21" t="s">
+      <c r="G207" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="H207" s="24">
+      <c r="H207" s="21">
         <v>349400</v>
       </c>
       <c r="I207" s="5" t="s">
@@ -8667,17 +8654,17 @@
       </c>
       <c r="J207" s="14"/>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A208" s="20">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A208" s="18">
         <v>12</v>
       </c>
-      <c r="B208" s="20">
+      <c r="B208" s="18">
         <v>19</v>
       </c>
-      <c r="C208" s="19">
+      <c r="C208" s="18">
         <v>15</v>
       </c>
-      <c r="D208" s="19" t="s">
+      <c r="D208" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E208" s="5" t="s">
@@ -8697,17 +8684,17 @@
       </c>
       <c r="J208" s="14"/>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A209" s="20">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A209" s="18">
         <v>8</v>
       </c>
-      <c r="B209" s="20">
+      <c r="B209" s="18">
         <v>13</v>
       </c>
-      <c r="C209" s="19">
+      <c r="C209" s="18">
         <v>16</v>
       </c>
-      <c r="D209" s="19" t="s">
+      <c r="D209" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E209" s="5" t="s">
@@ -8727,17 +8714,17 @@
       </c>
       <c r="J209" s="14"/>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A210" s="20">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A210" s="18">
         <v>13</v>
       </c>
-      <c r="B210" s="23">
+      <c r="B210" s="20">
         <v>12</v>
       </c>
-      <c r="C210" s="19">
+      <c r="C210" s="18">
         <v>17</v>
       </c>
-      <c r="D210" s="19" t="s">
+      <c r="D210" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E210" s="5" t="s">
@@ -8757,17 +8744,17 @@
       </c>
       <c r="J210" s="14"/>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A211" s="20">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A211" s="18">
         <v>21</v>
       </c>
-      <c r="B211" s="23">
+      <c r="B211" s="20">
         <v>12</v>
       </c>
-      <c r="C211" s="19">
+      <c r="C211" s="18">
         <v>18</v>
       </c>
-      <c r="D211" s="19" t="s">
+      <c r="D211" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E211" s="5" t="s">
@@ -8787,47 +8774,47 @@
       </c>
       <c r="J211" s="14"/>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A212" s="17">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A212" s="16">
         <v>16</v>
       </c>
-      <c r="B212" s="25">
+      <c r="B212" s="22">
         <v>11</v>
       </c>
-      <c r="C212" s="17">
+      <c r="C212" s="16">
         <v>19</v>
       </c>
-      <c r="D212" s="17" t="s">
+      <c r="D212" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E212" s="18" t="s">
+      <c r="E212" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="F212" s="18" t="s">
+      <c r="F212" s="17" t="s">
         <v>242</v>
       </c>
-      <c r="G212" s="18" t="s">
+      <c r="G212" s="17" t="s">
         <v>243</v>
       </c>
-      <c r="H212" s="43">
+      <c r="H212" s="37">
         <v>120000</v>
       </c>
-      <c r="I212" s="18" t="s">
+      <c r="I212" s="17" t="s">
         <v>406</v>
       </c>
       <c r="J212" s="14"/>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A213" s="20">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A213" s="18">
         <v>15</v>
       </c>
-      <c r="B213" s="23">
+      <c r="B213" s="20">
         <v>10</v>
       </c>
-      <c r="C213" s="19">
+      <c r="C213" s="18">
         <v>20</v>
       </c>
-      <c r="D213" s="19" t="s">
+      <c r="D213" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E213" s="5" t="s">
@@ -8847,17 +8834,17 @@
       </c>
       <c r="J213" s="14"/>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A214" s="20">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A214" s="18">
         <v>6</v>
       </c>
-      <c r="B214" s="23">
+      <c r="B214" s="20">
         <v>9</v>
       </c>
-      <c r="C214" s="19">
+      <c r="C214" s="18">
         <v>21</v>
       </c>
-      <c r="D214" s="19" t="s">
+      <c r="D214" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E214" s="5" t="s">
@@ -8877,50 +8864,50 @@
       </c>
       <c r="J214" s="14"/>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A215" s="17">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A215" s="16">
         <v>7</v>
       </c>
-      <c r="B215" s="25">
+      <c r="B215" s="22">
         <v>9</v>
       </c>
-      <c r="C215" s="17">
+      <c r="C215" s="16">
         <v>22</v>
       </c>
-      <c r="D215" s="17" t="s">
+      <c r="D215" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="E215" s="18" t="s">
+      <c r="E215" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="F215" s="18" t="s">
+      <c r="F215" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="G215" s="18" t="s">
+      <c r="G215" s="17" t="s">
         <v>253</v>
       </c>
-      <c r="H215" s="43">
+      <c r="H215" s="37">
         <v>34500</v>
       </c>
-      <c r="I215" s="18" t="s">
+      <c r="I215" s="17" t="s">
         <v>406</v>
       </c>
-      <c r="J215" s="22">
+      <c r="J215" s="19">
         <f>SUM(H194:H198,H202:H203,H212,H215)</f>
         <v>21945700</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A216" s="20">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A216" s="18">
         <v>23</v>
       </c>
-      <c r="B216" s="23">
+      <c r="B216" s="20">
         <v>8</v>
       </c>
-      <c r="C216" s="19">
+      <c r="C216" s="18">
         <v>23</v>
       </c>
-      <c r="D216" s="19" t="s">
+      <c r="D216" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E216" s="5" t="s">
@@ -8940,17 +8927,17 @@
       </c>
       <c r="J216" s="14"/>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A217" s="20">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A217" s="18">
         <v>20</v>
       </c>
-      <c r="B217" s="23">
+      <c r="B217" s="20">
         <v>8</v>
       </c>
-      <c r="C217" s="19">
+      <c r="C217" s="18">
         <v>24</v>
       </c>
-      <c r="D217" s="19" t="s">
+      <c r="D217" s="18" t="s">
         <v>402</v>
       </c>
       <c r="E217" s="5" t="s">
@@ -8970,35 +8957,35 @@
       </c>
       <c r="J217" s="14"/>
     </row>
-    <row r="218" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A218" s="31">
+    <row r="218" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A218" s="27">
         <v>9</v>
       </c>
-      <c r="B218" s="35">
+      <c r="B218" s="30">
         <v>8</v>
       </c>
-      <c r="C218" s="32">
+      <c r="C218" s="27">
         <v>25</v>
       </c>
-      <c r="D218" s="32" t="s">
-        <v>402</v>
-      </c>
-      <c r="E218" s="33" t="s">
+      <c r="D218" s="27" t="s">
+        <v>402</v>
+      </c>
+      <c r="E218" s="28" t="s">
         <v>220</v>
       </c>
-      <c r="F218" s="33" t="s">
+      <c r="F218" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="G218" s="33" t="s">
+      <c r="G218" s="28" t="s">
         <v>237</v>
       </c>
-      <c r="H218" s="34">
+      <c r="H218" s="29">
         <v>101400</v>
       </c>
-      <c r="I218" s="33" t="s">
-        <v>407</v>
-      </c>
-      <c r="J218" s="34"/>
+      <c r="I218" s="28" t="s">
+        <v>407</v>
+      </c>
+      <c r="J218" s="29"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
@@ -9012,15 +8999,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:D43"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" customWidth="1"/>
+    <col min="1" max="1" width="16.5546875" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" customWidth="1"/>
     <col min="3" max="3" width="19" style="2" customWidth="1"/>
-    <col min="4" max="5" width="14.5703125" customWidth="1"/>
+    <col min="4" max="5" width="14.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:4" s="9" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" s="9" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="8" t="s">
         <v>394</v>
@@ -9030,7 +9017,7 @@
       </c>
       <c r="D2" s="7"/>
     </row>
-    <row r="3" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>389</v>
       </c>
@@ -9045,7 +9032,7 @@
         <v>0.64140134409789218</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>390</v>
       </c>
@@ -9060,7 +9047,7 @@
         <v>9.1456557595396268E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>391</v>
       </c>
@@ -9075,7 +9062,7 @@
         <v>0.17211091643159057</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>392</v>
       </c>
@@ -9090,7 +9077,7 @@
         <v>9.5031181875121024E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="10">
         <f>SUM(B3:B6)</f>
@@ -9105,7 +9092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="5"/>
       <c r="B33" s="12" t="s">
         <v>393</v>
@@ -9114,7 +9101,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
         <v>119</v>
       </c>
@@ -9123,7 +9110,7 @@
       </c>
       <c r="C34" s="14"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
         <v>191</v>
       </c>
@@ -9132,7 +9119,7 @@
       </c>
       <c r="C35" s="14"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
         <v>336</v>
       </c>
@@ -9141,7 +9128,7 @@
       </c>
       <c r="C36" s="14"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
         <v>165</v>
       </c>
@@ -9150,7 +9137,7 @@
       </c>
       <c r="C37" s="14"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
         <v>45</v>
       </c>
@@ -9159,7 +9146,7 @@
       </c>
       <c r="C38" s="14"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
         <v>262</v>
       </c>
@@ -9168,7 +9155,7 @@
       </c>
       <c r="C39" s="14"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
         <v>4</v>
       </c>
@@ -9177,7 +9164,7 @@
       </c>
       <c r="C40" s="14"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
         <v>149</v>
       </c>
@@ -9186,7 +9173,7 @@
       </c>
       <c r="C41" s="14"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
         <v>220</v>
       </c>
@@ -9195,7 +9182,7 @@
       </c>
       <c r="C42" s="14"/>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="5"/>
       <c r="B43" s="10">
         <f>SUM(B34:B42)</f>
